--- a/site/leagues/betclic/2026_2027/xlsx/shot_packs/shot_pack_VSC.xlsx
+++ b/site/leagues/betclic/2026_2027/xlsx/shot_packs/shot_pack_VSC.xlsx
@@ -21,14 +21,14 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'overview'!$A$1:$W$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'alerts'!$A$1:$B$6</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'players_volume'!$A$1:$S$7</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'players_eff'!$A$1:$S$6</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'players_3pt_volume'!$A$1:$N$7</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'players_3pt_pct'!$A$1:$A$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'players_volume'!$A$1:$S$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'players_eff'!$A$1:$S$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'players_3pt_volume'!$A$1:$N$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'players_3pt_pct'!$A$1:$N$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'team_zones'!$A$1:$I$7</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'preferred_areas'!$A$1:$P$7</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'player_zones_volume'!$A$1:$K$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'player_zones_pct'!$A$1:$A$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'preferred_areas'!$A$1:$P$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'player_zones_volume'!$A$1:$K$14</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'player_zones_pct'!$A$1:$K$6</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -448,7 +448,7 @@
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
     <col width="14" customWidth="1" min="12" max="12"/>
-    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="17" customWidth="1" min="13" max="13"/>
     <col width="16" customWidth="1" min="14" max="14"/>
     <col width="16" customWidth="1" min="15" max="15"/>
     <col width="19" customWidth="1" min="16" max="16"/>
@@ -590,29 +590,29 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>64</v>
+        <v>128</v>
       </c>
       <c r="D2" t="n">
-        <v>28</v>
+        <v>53</v>
       </c>
       <c r="E2" t="n">
-        <v>64</v>
+        <v>122</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>43.8%</t>
+          <t>41.4%</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>46.2%</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>24</v>
+        <v>48</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -629,15 +629,15 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="N2" t="n">
-        <v>17</v>
+        <v>42</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>47.1%</t>
+          <t>59.5%</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -646,27 +646,27 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>17</v>
+        <v>36</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>23.5%</t>
+          <t>30.6%</t>
         </is>
       </c>
       <c r="S2" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T2" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="U2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V2" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="W2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -681,28 +681,306 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:K6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="11" customWidth="1" min="1" max="1"/>
+    <col width="19" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="28" customWidth="1" min="10" max="10"/>
+    <col width="25" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>info</t>
+          <t>player_id</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>player_name</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>zone</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>attempts</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>made</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>points</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>fg_pct</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>pps</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>zone_share</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>player_zone_rank_by_volume</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>player_zone_rank_by_pct</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>sem dados</t>
-        </is>
+          <t>VSC_M._HOUGE</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>M. Houge</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>8</v>
+      </c>
+      <c r="E2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F2" t="n">
+        <v>10</v>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>62.5%</t>
+        </is>
+      </c>
+      <c r="H2" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>88.9%</t>
+        </is>
+      </c>
+      <c r="J2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>VSC_K._WARNER</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>K. Warner</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>8</v>
+      </c>
+      <c r="E3" t="n">
+        <v>3</v>
+      </c>
+      <c r="F3" t="n">
+        <v>9</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>37.5%</t>
+        </is>
+      </c>
+      <c r="H3" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>47.1%</t>
+        </is>
+      </c>
+      <c r="J3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K3" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>VSC_D._RUNGE</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>D. Runge</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>9</v>
+      </c>
+      <c r="E4" t="n">
+        <v>3</v>
+      </c>
+      <c r="F4" t="n">
+        <v>9</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="H4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>56.2%</t>
+        </is>
+      </c>
+      <c r="J4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>VSC_T._SIMAO</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>T. Simao</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>11</v>
+      </c>
+      <c r="E5" t="n">
+        <v>3</v>
+      </c>
+      <c r="F5" t="n">
+        <v>6</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>27.3%</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="J5" t="n">
+        <v>1</v>
+      </c>
+      <c r="K5" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>VSC_M._DRUMWRIGHT</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>M. Drumwright</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>8</v>
+      </c>
+      <c r="E6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F6" t="n">
+        <v>2</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>12.5%</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>34.8%</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
+        <v>1</v>
+      </c>
+      <c r="K6" t="n">
+        <v>3</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:A2"/>
+  <autoFilter ref="A1:K6"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -740,7 +1018,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Maior volume: M. Drumwright (15 L)</t>
+          <t>Maior volume: M. Drumwright (23 L)</t>
         </is>
       </c>
     </row>
@@ -752,7 +1030,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Maior volume 3pt: D. Runge (7 3PA)</t>
+          <t>Maior volume 3pt: D. Runge (10 3PA)</t>
         </is>
       </c>
     </row>
@@ -764,7 +1042,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Mais eficaz: A. Guedes (1.4 pts/shot)</t>
+          <t>Mais eficaz: A. Guedes (1.3 pts/shot)</t>
         </is>
       </c>
     </row>
@@ -776,7 +1054,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Zona mais usada: Paint Non-RA (17 L)</t>
+          <t>Zona mais usada: Restricted Area (42 L)</t>
         </is>
       </c>
     </row>
@@ -788,7 +1066,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Zona mais eficaz: Restricted Area (66.7%)</t>
+          <t>Zona mais eficaz: Restricted Area (59.5%)</t>
         </is>
       </c>
     </row>
@@ -804,7 +1082,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S7"/>
+  <dimension ref="A1:S10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -937,30 +1215,30 @@
         </is>
       </c>
       <c r="C2" t="n">
+        <v>23</v>
+      </c>
+      <c r="D2" t="n">
+        <v>7</v>
+      </c>
+      <c r="E2" t="n">
         <v>15</v>
       </c>
-      <c r="D2" t="n">
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>30.4%</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
         <v>5</v>
       </c>
-      <c r="E2" t="n">
-        <v>11</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>33.3%</t>
-        </is>
-      </c>
-      <c r="G2" t="n">
-        <v>4</v>
-      </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>20.0%</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>26.7%</t>
+          <t>21.7%</t>
         </is>
       </c>
       <c r="J2" t="n">
@@ -972,76 +1250,76 @@
         </is>
       </c>
       <c r="L2" t="n">
+        <v>8</v>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>12.5%</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="O2" t="n">
         <v>7</v>
       </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>14.3%</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
-        </is>
-      </c>
-      <c r="O2" t="n">
-        <v>4</v>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>57.1%</t>
         </is>
       </c>
       <c r="Q2" t="n">
         <v>1</v>
       </c>
       <c r="R2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="S2" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>VSC_T._SIMAO</t>
+          <t>VSC_R._STEIN</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>T. Simao</t>
+          <t>R. Stein</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="D3" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E3" t="n">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>38.5%</t>
+          <t>45.5%</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>28.6%</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>23.1%</t>
+          <t>31.8%</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -1053,27 +1331,27 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>83.3%</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Mid-Range</t>
         </is>
       </c>
       <c r="O3" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="Q3" t="n">
         <v>2</v>
       </c>
       <c r="R3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S3" t="n">
         <v>4</v>
@@ -1082,120 +1360,120 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>VSC_D._RUNGE</t>
+          <t>VSC_T._SIMAO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>D. Runge</t>
+          <t>T. Simao</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="D4" t="n">
+        <v>7</v>
+      </c>
+      <c r="E4" t="n">
+        <v>16</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>31.8%</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
         <v>6</v>
       </c>
-      <c r="E4" t="n">
-        <v>15</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>50.0%</t>
-        </is>
-      </c>
-      <c r="G4" t="n">
-        <v>7</v>
-      </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>42.9%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>58.3%</t>
+          <t>27.3%</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>1.2</v>
+        <v>0.7</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="L4" t="n">
+        <v>11</v>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>27.3%</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
           <t>Above the Break 3</t>
         </is>
       </c>
-      <c r="L4" t="n">
-        <v>7</v>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>42.9%</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>Restricted Area</t>
-        </is>
-      </c>
       <c r="O4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R4" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="S4" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>VSC_A._GUEDES</t>
+          <t>VSC_K._WARNER</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>A. Guedes</t>
+          <t>K. Warner</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="D5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E5" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>54.5%</t>
+          <t>41.2%</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>54.5%</t>
+          <t>52.9%</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>1.4</v>
+        <v>1</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -1203,31 +1481,31 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>37.5%</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>Corner 3 Left</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="O5" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>80.0%</t>
         </is>
       </c>
       <c r="Q5" t="n">
         <v>4</v>
       </c>
       <c r="R5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="S5" t="n">
         <v>2</v>
@@ -1236,159 +1514,376 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>VSC_R._STEIN</t>
+          <t>VSC_D._RUNGE</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>R. Stein</t>
+          <t>D. Runge</t>
         </is>
       </c>
       <c r="C6" t="n">
+        <v>16</v>
+      </c>
+      <c r="D6" t="n">
+        <v>8</v>
+      </c>
+      <c r="E6" t="n">
+        <v>20</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
         <v>10</v>
       </c>
-      <c r="D6" t="n">
-        <v>5</v>
-      </c>
-      <c r="E6" t="n">
-        <v>11</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>50.0%</t>
-        </is>
-      </c>
-      <c r="G6" t="n">
-        <v>2</v>
-      </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>62.5%</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>Mid-Range</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="L6" t="n">
+        <v>9</v>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="O6" t="n">
         <v>4</v>
       </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>25.0%</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>Restricted Area</t>
-        </is>
-      </c>
-      <c r="O6" t="n">
-        <v>2</v>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>75.0%</t>
         </is>
       </c>
       <c r="Q6" t="n">
         <v>5</v>
       </c>
       <c r="R6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>VSC_R._COSTA</t>
+          <t>VSC_A._GUEDES</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>R. Costa</t>
+          <t>A. Guedes</t>
         </is>
       </c>
       <c r="C7" t="n">
+        <v>15</v>
+      </c>
+      <c r="D7" t="n">
+        <v>8</v>
+      </c>
+      <c r="E7" t="n">
+        <v>20</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>53.3%</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>8</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>53.3%</t>
+        </is>
+      </c>
+      <c r="J7" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="L7" t="n">
+        <v>5</v>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>20.0%</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="O7" t="n">
         <v>3</v>
       </c>
-      <c r="D7" t="n">
-        <v>1</v>
-      </c>
-      <c r="E7" t="n">
-        <v>2</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>33.3%</t>
-        </is>
-      </c>
-      <c r="G7" t="n">
-        <v>2</v>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>66.7%</t>
-        </is>
-      </c>
-      <c r="J7" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>Paint Non-RA</t>
-        </is>
-      </c>
-      <c r="L7" t="n">
-        <v>1</v>
-      </c>
-      <c r="M7" t="inlineStr">
+      <c r="P7" t="inlineStr">
         <is>
           <t>100.0%</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>Corner 3 Left</t>
-        </is>
-      </c>
-      <c r="O7" t="n">
-        <v>1</v>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>0.0%</t>
         </is>
       </c>
       <c r="Q7" t="n">
         <v>6</v>
       </c>
       <c r="R7" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="S7" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>VSC_M._HOUGE</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>M. Houge</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>9</v>
+      </c>
+      <c r="D8" t="n">
         <v>5</v>
       </c>
+      <c r="E8" t="n">
+        <v>10</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>55.6%</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="L8" t="n">
+        <v>8</v>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>62.5%</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>Mid-Range</t>
+        </is>
+      </c>
+      <c r="O8" t="n">
+        <v>1</v>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>7</v>
+      </c>
+      <c r="R8" t="n">
+        <v>3</v>
+      </c>
+      <c r="S8" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>VSC_R._COSTA</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>R. Costa</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>3</v>
+      </c>
+      <c r="D9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E9" t="n">
+        <v>2</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>2</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>66.7%</t>
+        </is>
+      </c>
+      <c r="J9" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="L9" t="n">
+        <v>1</v>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>Corner 3 Left</t>
+        </is>
+      </c>
+      <c r="O9" t="n">
+        <v>1</v>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>8</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7</v>
+      </c>
+      <c r="S9" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>VSC_S._VERDE</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>S. Verde</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>1</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>1</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Corner 3 Right</t>
+        </is>
+      </c>
+      <c r="L10" t="n">
+        <v>1</v>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="inlineStr"/>
+      <c r="Q10" t="n">
+        <v>9</v>
+      </c>
+      <c r="R10" t="n">
+        <v>9</v>
+      </c>
+      <c r="S10" t="n">
+        <v>8</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:S7"/>
+  <autoFilter ref="A1:S10"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1399,7 +1894,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S6"/>
+  <dimension ref="A1:S7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -1532,66 +2027,66 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>54.5%</t>
+          <t>53.3%</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="F2" t="n">
+        <v>8</v>
+      </c>
+      <c r="G2" t="n">
+        <v>20</v>
+      </c>
+      <c r="H2" t="n">
+        <v>8</v>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>53.3%</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="L2" t="n">
+        <v>5</v>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>20.0%</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="O2" t="n">
+        <v>3</v>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="Q2" t="n">
+        <v>1</v>
+      </c>
+      <c r="R2" t="n">
         <v>6</v>
-      </c>
-      <c r="G2" t="n">
-        <v>15</v>
-      </c>
-      <c r="H2" t="n">
-        <v>6</v>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>50.0%</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>54.5%</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
-        </is>
-      </c>
-      <c r="L2" t="n">
-        <v>3</v>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>Corner 3 Left</t>
-        </is>
-      </c>
-      <c r="O2" t="n">
-        <v>2</v>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="Q2" t="n">
-        <v>1</v>
-      </c>
-      <c r="R2" t="n">
-        <v>4</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -1617,25 +2112,25 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="F3" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G3" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="H3" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>42.9%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>58.3%</t>
+          <t>62.5%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1644,11 +2139,11 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>42.9%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -1657,21 +2152,21 @@
         </is>
       </c>
       <c r="O3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>75.0%</t>
         </is>
       </c>
       <c r="Q3" t="n">
         <v>2</v>
       </c>
       <c r="R3" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="S3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4">
@@ -1686,157 +2181,157 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>45.5%</t>
         </is>
       </c>
       <c r="E4" t="n">
+        <v>22</v>
+      </c>
+      <c r="F4" t="n">
         <v>10</v>
       </c>
-      <c r="F4" t="n">
-        <v>5</v>
-      </c>
       <c r="G4" t="n">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="H4" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>28.6%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>31.8%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="L4" t="n">
+        <v>6</v>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>83.3%</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
           <t>Mid-Range</t>
         </is>
       </c>
-      <c r="L4" t="n">
-        <v>4</v>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>25.0%</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>Restricted Area</t>
-        </is>
-      </c>
       <c r="O4" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="Q4" t="n">
         <v>3</v>
       </c>
       <c r="R4" t="n">
+        <v>2</v>
+      </c>
+      <c r="S4" t="n">
         <v>5</v>
-      </c>
-      <c r="S4" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>VSC_T._SIMAO</t>
+          <t>VSC_K._WARNER</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>T. Simao</t>
+          <t>K. Warner</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>38.5%</t>
+          <t>41.2%</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="F5" t="n">
+        <v>7</v>
+      </c>
+      <c r="G5" t="n">
+        <v>17</v>
+      </c>
+      <c r="H5" t="n">
+        <v>9</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>52.9%</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="L5" t="n">
+        <v>8</v>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>37.5%</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="O5" t="n">
         <v>5</v>
       </c>
-      <c r="G5" t="n">
-        <v>10</v>
-      </c>
-      <c r="H5" t="n">
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>80.0%</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
         <v>3</v>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>23.1%</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>Restricted Area</t>
-        </is>
-      </c>
-      <c r="L5" t="n">
-        <v>6</v>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>50.0%</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>Paint Non-RA</t>
-        </is>
-      </c>
-      <c r="O5" t="n">
+      <c r="R5" t="n">
         <v>4</v>
       </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>50.0%</t>
-        </is>
-      </c>
-      <c r="Q5" t="n">
-        <v>4</v>
-      </c>
-      <c r="R5" t="n">
-        <v>2</v>
-      </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>VSC_M._DRUMWRIGHT</t>
+          <t>VSC_T._SIMAO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>M. Drumwright</t>
+          <t>T. Simao</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -1844,69 +2339,146 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
+          <t>31.8%</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>22</v>
+      </c>
+      <c r="F6" t="n">
+        <v>7</v>
+      </c>
+      <c r="G6" t="n">
+        <v>16</v>
+      </c>
+      <c r="H6" t="n">
+        <v>6</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
           <t>33.3%</t>
         </is>
       </c>
-      <c r="E6" t="n">
-        <v>15</v>
-      </c>
-      <c r="F6" t="n">
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>27.3%</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="L6" t="n">
+        <v>11</v>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>27.3%</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="O6" t="n">
         <v>5</v>
       </c>
-      <c r="G6" t="n">
-        <v>11</v>
-      </c>
-      <c r="H6" t="n">
-        <v>4</v>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>25.0%</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>26.7%</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>Paint Non-RA</t>
-        </is>
-      </c>
-      <c r="L6" t="n">
-        <v>7</v>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>14.3%</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
-        </is>
-      </c>
-      <c r="O6" t="n">
-        <v>4</v>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="Q6" t="n">
         <v>5</v>
       </c>
       <c r="R6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S6" t="n">
-        <v>4</v>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>VSC_M._DRUMWRIGHT</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>M. Drumwright</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>30.4%</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>23</v>
+      </c>
+      <c r="F7" t="n">
+        <v>7</v>
+      </c>
+      <c r="G7" t="n">
+        <v>15</v>
+      </c>
+      <c r="H7" t="n">
+        <v>5</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>20.0%</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>21.7%</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="L7" t="n">
+        <v>8</v>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>12.5%</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="O7" t="n">
+        <v>7</v>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>57.1%</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>6</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1</v>
+      </c>
+      <c r="S7" t="n">
+        <v>6</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:S6"/>
+  <autoFilter ref="A1:S7"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1917,7 +2489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N7"/>
+  <dimension ref="A1:N10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -2020,26 +2592,26 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>42.9%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>58.3%</t>
+          <t>62.5%</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="H2" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="I2" t="n">
         <v>1.2</v>
@@ -2050,55 +2622,55 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>42.9%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="M2" t="n">
         <v>1</v>
       </c>
       <c r="N2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>VSC_A._GUEDES</t>
+          <t>VSC_K._WARNER</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>A. Guedes</t>
+          <t>K. Warner</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D3" t="n">
         <v>3</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>54.5%</t>
+          <t>52.9%</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="H3" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="I3" t="n">
-        <v>1.4</v>
+        <v>1</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -2106,111 +2678,111 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>37.5%</t>
         </is>
       </c>
       <c r="M3" t="n">
         <v>2</v>
       </c>
       <c r="N3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>VSC_M._DRUMWRIGHT</t>
+          <t>VSC_A._GUEDES</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>M. Drumwright</t>
+          <t>A. Guedes</t>
         </is>
       </c>
       <c r="C4" t="n">
+        <v>8</v>
+      </c>
+      <c r="D4" t="n">
         <v>4</v>
       </c>
-      <c r="D4" t="n">
-        <v>1</v>
-      </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>26.7%</t>
+          <t>53.3%</t>
         </is>
       </c>
       <c r="G4" t="n">
         <v>15</v>
       </c>
       <c r="H4" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="I4" t="n">
-        <v>0.7</v>
+        <v>1.3</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="K4" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>14.3%</t>
+          <t>20.0%</t>
         </is>
       </c>
       <c r="M4" t="n">
         <v>3</v>
       </c>
       <c r="N4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>VSC_T._SIMAO</t>
+          <t>VSC_R._STEIN</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>T. Simao</t>
+          <t>R. Stein</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>28.6%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>23.1%</t>
+          <t>31.8%</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="H5" t="n">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="I5" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -2222,7 +2794,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>83.3%</t>
         </is>
       </c>
       <c r="M5" t="n">
@@ -2235,91 +2807,91 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>VSC_R._STEIN</t>
+          <t>VSC_T._SIMAO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>R. Stein</t>
+          <t>T. Simao</t>
         </is>
       </c>
       <c r="C6" t="n">
+        <v>6</v>
+      </c>
+      <c r="D6" t="n">
         <v>2</v>
       </c>
-      <c r="D6" t="n">
-        <v>1</v>
-      </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>27.3%</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="H6" t="n">
+        <v>16</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="K6" t="n">
         <v>11</v>
       </c>
-      <c r="I6" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>Mid-Range</t>
-        </is>
-      </c>
-      <c r="K6" t="n">
-        <v>4</v>
-      </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>27.3%</t>
         </is>
       </c>
       <c r="M6" t="n">
         <v>5</v>
       </c>
       <c r="N6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>VSC_R._COSTA</t>
+          <t>VSC_M._DRUMWRIGHT</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>R. Costa</t>
+          <t>M. Drumwright</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>20.0%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>21.7%</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>3</v>
+        <v>23</v>
       </c>
       <c r="H7" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="I7" t="n">
         <v>0.7</v>
@@ -2330,22 +2902,184 @@
         </is>
       </c>
       <c r="K7" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
+          <t>12.5%</t>
+        </is>
+      </c>
+      <c r="M7" t="n">
+        <v>6</v>
+      </c>
+      <c r="N7" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>VSC_R._COSTA</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>R. Costa</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>2</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>66.7%</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>3</v>
+      </c>
+      <c r="H8" t="n">
+        <v>2</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="K8" t="n">
+        <v>1</v>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
           <t>100.0%</t>
         </is>
       </c>
-      <c r="M7" t="n">
-        <v>5</v>
-      </c>
-      <c r="N7" t="n">
-        <v>5</v>
-      </c>
+      <c r="M8" t="n">
+        <v>7</v>
+      </c>
+      <c r="N8" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>VSC_S._VERDE</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>S. Verde</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>1</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Corner 3 Right</t>
+        </is>
+      </c>
+      <c r="K9" t="n">
+        <v>1</v>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="M9" t="n">
+        <v>8</v>
+      </c>
+      <c r="N9" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>VSC_M._HOUGE</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>M. Houge</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>9</v>
+      </c>
+      <c r="H10" t="n">
+        <v>10</v>
+      </c>
+      <c r="I10" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="K10" t="n">
+        <v>8</v>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>62.5%</t>
+        </is>
+      </c>
+      <c r="M10" t="n">
+        <v>9</v>
+      </c>
+      <c r="N10" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N7"/>
+  <autoFilter ref="A1:N10"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2356,28 +3090,155 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:N2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="11" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="19" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="19" customWidth="1" min="10" max="10"/>
+    <col width="16" customWidth="1" min="11" max="11"/>
+    <col width="16" customWidth="1" min="12" max="12"/>
+    <col width="22" customWidth="1" min="13" max="13"/>
+    <col width="19" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>info</t>
+          <t>player_id</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>player_name</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>fg3a</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>fg3m</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>fg3_pct</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>three_rate</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>shot_attempts</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>points_from_shots</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>pts_per_shot</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>top_zone_1</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>top_zone_1_att</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>top_zone_1_pct</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>team_rank_3pt_volume</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>team_rank_3pt_pct</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>sem dados</t>
-        </is>
+          <t>VSC_D._RUNGE</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>D. Runge</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>10</v>
+      </c>
+      <c r="D2" t="n">
+        <v>4</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>40.0%</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>62.5%</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>16</v>
+      </c>
+      <c r="H2" t="n">
+        <v>20</v>
+      </c>
+      <c r="I2" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="K2" t="n">
+        <v>9</v>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="M2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N2" t="n">
+        <v>2</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:A2"/>
+  <autoFilter ref="A1:N2"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2452,36 +3313,36 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>17</v>
+        <v>42</v>
       </c>
       <c r="C2" t="n">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="D2" t="n">
-        <v>16</v>
+        <v>50</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>47.1%</t>
+          <t>59.5%</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>0.9</v>
+        <v>1.2</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>26.6%</t>
+          <t>32.8%</t>
         </is>
       </c>
       <c r="H2" t="n">
         <v>1</v>
       </c>
       <c r="I2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -2491,29 +3352,29 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>17</v>
+        <v>36</v>
       </c>
       <c r="C3" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="D3" t="n">
-        <v>12</v>
+        <v>33</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>23.5%</t>
+          <t>30.6%</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>26.6%</t>
+          <t>28.1%</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I3" t="n">
         <v>3</v>
@@ -2522,36 +3383,36 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>Paint Non-RA</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="C4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D4" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>37.5%</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.3</v>
+        <v>0.8</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>23.4%</t>
+          <t>18.8%</t>
         </is>
       </c>
       <c r="H4" t="n">
         <v>3</v>
       </c>
       <c r="I4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5">
@@ -2561,32 +3422,32 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="C5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D5" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>21.4%</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>10.9%</t>
         </is>
       </c>
       <c r="H5" t="n">
         <v>4</v>
       </c>
       <c r="I5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6">
@@ -2596,25 +3457,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D6" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>7.8%</t>
+          <t>6.2%</t>
         </is>
       </c>
       <c r="H6" t="n">
@@ -2631,7 +3492,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C7" t="n">
         <v>1</v>
@@ -2641,11 +3502,11 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.5</v>
+        <v>0.8</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -2656,7 +3517,7 @@
         <v>6</v>
       </c>
       <c r="I7" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -2671,7 +3532,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P7"/>
+  <dimension ref="A1:P10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -2791,53 +3652,53 @@
         </is>
       </c>
       <c r="D2" t="n">
+        <v>8</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>12.5%</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
         <v>7</v>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>14.3%</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>57.1%</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
         <is>
           <t>Above the Break 3</t>
         </is>
       </c>
-      <c r="G2" t="n">
-        <v>4</v>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>25.0%</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>Restricted Area</t>
-        </is>
-      </c>
       <c r="J2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>20.0%</t>
         </is>
       </c>
       <c r="L2" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>30.4%</t>
         </is>
       </c>
       <c r="N2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>20.0%</t>
         </is>
       </c>
       <c r="P2" t="n">
@@ -2847,12 +3708,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>VSC_T._SIMAO</t>
+          <t>VSC_R._STEIN</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>T. Simao</t>
+          <t>R. Stein</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -2865,90 +3726,90 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>83.3%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Mid-Range</t>
         </is>
       </c>
       <c r="G3" t="n">
+        <v>6</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="J3" t="n">
         <v>4</v>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>50.0%</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
-        </is>
-      </c>
-      <c r="J3" t="n">
-        <v>2</v>
-      </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="L3" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>38.5%</t>
+          <t>45.5%</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>28.6%</t>
         </is>
       </c>
       <c r="P3" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>VSC_D._RUNGE</t>
+          <t>VSC_T._SIMAO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>D. Runge</t>
+          <t>T. Simao</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>11</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>27.3%</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
           <t>Above the Break 3</t>
         </is>
       </c>
-      <c r="D4" t="n">
-        <v>7</v>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>42.9%</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Restricted Area</t>
-        </is>
-      </c>
       <c r="G4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -2957,42 +3818,42 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="L4" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>31.8%</t>
         </is>
       </c>
       <c r="N4" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>42.9%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="P4" t="n">
-        <v>1.2</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>VSC_A._GUEDES</t>
+          <t>VSC_K._WARNER</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>A. Guedes</t>
+          <t>K. Warner</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -3001,201 +3862,377 @@
         </is>
       </c>
       <c r="D5" t="n">
+        <v>8</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>37.5%</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>5</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>80.0%</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="J5" t="n">
         <v>3</v>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Corner 3 Left</t>
-        </is>
-      </c>
-      <c r="G5" t="n">
-        <v>2</v>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>Paint Non-RA</t>
-        </is>
-      </c>
-      <c r="J5" t="n">
-        <v>2</v>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
       <c r="L5" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>54.5%</t>
+          <t>41.2%</t>
         </is>
       </c>
       <c r="N5" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="P5" t="n">
-        <v>1.4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>VSC_R._STEIN</t>
+          <t>VSC_D._RUNGE</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>R. Stein</t>
+          <t>D. Runge</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Mid-Range</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="D6" t="n">
+        <v>9</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
         <v>4</v>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>25.0%</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Restricted Area</t>
-        </is>
-      </c>
-      <c r="G6" t="n">
-        <v>2</v>
-      </c>
       <c r="H6" t="inlineStr">
         <is>
+          <t>75.0%</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Corner 3 Left</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
+        <v>1</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
           <t>100.0%</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>Paint Non-RA</t>
-        </is>
-      </c>
-      <c r="J6" t="n">
-        <v>2</v>
-      </c>
-      <c r="K6" t="inlineStr">
+      <c r="L6" t="n">
+        <v>16</v>
+      </c>
+      <c r="M6" t="inlineStr">
         <is>
           <t>50.0%</t>
         </is>
       </c>
-      <c r="L6" t="n">
+      <c r="N6" t="n">
         <v>10</v>
       </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>50.0%</t>
-        </is>
-      </c>
-      <c r="N6" t="n">
-        <v>2</v>
-      </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="P6" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>VSC_A._GUEDES</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>A. Guedes</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>5</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>20.0%</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>3</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Mid-Range</t>
+        </is>
+      </c>
+      <c r="J7" t="n">
+        <v>3</v>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="L7" t="n">
+        <v>15</v>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>53.3%</t>
+        </is>
+      </c>
+      <c r="N7" t="n">
+        <v>8</v>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="P7" t="n">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>VSC_M._HOUGE</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>M. Houge</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>8</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>62.5%</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Mid-Range</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="n">
+        <v>9</v>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>55.6%</t>
+        </is>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="n">
+        <v>1.1</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
           <t>VSC_R._COSTA</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>R. Costa</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>Paint Non-RA</t>
         </is>
       </c>
-      <c r="D7" t="n">
-        <v>1</v>
-      </c>
-      <c r="E7" t="inlineStr">
+      <c r="D9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E9" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>Corner 3 Left</t>
         </is>
       </c>
-      <c r="G7" t="n">
-        <v>1</v>
-      </c>
-      <c r="H7" t="inlineStr">
+      <c r="G9" t="n">
+        <v>1</v>
+      </c>
+      <c r="H9" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="I9" t="inlineStr">
         <is>
           <t>Corner 3 Right</t>
         </is>
       </c>
-      <c r="J7" t="n">
-        <v>1</v>
-      </c>
-      <c r="K7" t="inlineStr">
+      <c r="J9" t="n">
+        <v>1</v>
+      </c>
+      <c r="K9" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
-      <c r="L7" t="n">
+      <c r="L9" t="n">
         <v>3</v>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>33.3%</t>
         </is>
       </c>
-      <c r="N7" t="n">
+      <c r="N9" t="n">
         <v>2</v>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="O9" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
-      <c r="P7" t="n">
+      <c r="P9" t="n">
         <v>0.7</v>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>VSC_S._VERDE</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>S. Verde</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Corner 3 Right</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>1</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="n">
+        <v>1</v>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="N10" t="n">
+        <v>1</v>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:P7"/>
+  <autoFilter ref="A1:P10"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3206,7 +4243,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K4"/>
+  <dimension ref="A1:K14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -3282,84 +4319,84 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>VSC_D._RUNGE</t>
+          <t>VSC_T._SIMAO</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>D. Runge</t>
+          <t>T. Simao</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E2" t="n">
         <v>3</v>
       </c>
       <c r="F2" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>42.9%</t>
+          <t>27.3%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>1.3</v>
+        <v>0.5</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>58.3%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="J2" t="n">
         <v>1</v>
       </c>
       <c r="K2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>VSC_M._DRUMWRIGHT</t>
+          <t>VSC_D._RUNGE</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>M. Drumwright</t>
+          <t>D. Runge</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F3" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>14.3%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>0.3</v>
+        <v>1</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>46.7%</t>
+          <t>56.2%</t>
         </is>
       </c>
       <c r="J3" t="n">
@@ -3372,50 +4409,500 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>VSC_M._HOUGE</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>M. Houge</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>8</v>
+      </c>
+      <c r="E4" t="n">
+        <v>5</v>
+      </c>
+      <c r="F4" t="n">
+        <v>10</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>62.5%</t>
+        </is>
+      </c>
+      <c r="H4" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>88.9%</t>
+        </is>
+      </c>
+      <c r="J4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>VSC_K._WARNER</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>K. Warner</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>8</v>
+      </c>
+      <c r="E5" t="n">
+        <v>3</v>
+      </c>
+      <c r="F5" t="n">
+        <v>9</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>37.5%</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>47.1%</t>
+        </is>
+      </c>
+      <c r="J5" t="n">
+        <v>1</v>
+      </c>
+      <c r="K5" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>VSC_M._DRUMWRIGHT</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>M. Drumwright</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>8</v>
+      </c>
+      <c r="E6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F6" t="n">
+        <v>2</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>12.5%</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>34.8%</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
+        <v>1</v>
+      </c>
+      <c r="K6" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>VSC_M._DRUMWRIGHT</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>M. Drumwright</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>7</v>
+      </c>
+      <c r="E7" t="n">
+        <v>4</v>
+      </c>
+      <c r="F7" t="n">
+        <v>8</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>57.1%</t>
+        </is>
+      </c>
+      <c r="H7" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>30.4%</t>
+        </is>
+      </c>
+      <c r="J7" t="n">
+        <v>2</v>
+      </c>
+      <c r="K7" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>VSC_R._STEIN</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>R. Stein</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>6</v>
+      </c>
+      <c r="E8" t="n">
+        <v>5</v>
+      </c>
+      <c r="F8" t="n">
+        <v>10</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>83.3%</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>27.3%</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
+        <v>1</v>
+      </c>
+      <c r="K8" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>VSC_R._STEIN</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>R. Stein</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Mid-Range</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>6</v>
+      </c>
+      <c r="E9" t="n">
+        <v>2</v>
+      </c>
+      <c r="F9" t="n">
+        <v>4</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>27.3%</t>
+        </is>
+      </c>
+      <c r="J9" t="n">
+        <v>1</v>
+      </c>
+      <c r="K9" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>VSC_K._WARNER</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>K. Warner</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>5</v>
+      </c>
+      <c r="E10" t="n">
+        <v>4</v>
+      </c>
+      <c r="F10" t="n">
+        <v>8</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>80.0%</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>29.4%</t>
+        </is>
+      </c>
+      <c r="J10" t="n">
+        <v>2</v>
+      </c>
+      <c r="K10" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
           <t>VSC_T._SIMAO</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>T. Simao</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Restricted Area</t>
-        </is>
-      </c>
-      <c r="D4" t="n">
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>5</v>
+      </c>
+      <c r="E11" t="n">
+        <v>2</v>
+      </c>
+      <c r="F11" t="n">
         <v>6</v>
       </c>
-      <c r="E4" t="n">
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>40.0%</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>22.7%</t>
+        </is>
+      </c>
+      <c r="J11" t="n">
+        <v>2</v>
+      </c>
+      <c r="K11" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>VSC_T._SIMAO</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>T. Simao</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>5</v>
+      </c>
+      <c r="E12" t="n">
+        <v>2</v>
+      </c>
+      <c r="F12" t="n">
+        <v>4</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>40.0%</t>
+        </is>
+      </c>
+      <c r="H12" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>22.7%</t>
+        </is>
+      </c>
+      <c r="J12" t="n">
+        <v>2</v>
+      </c>
+      <c r="K12" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>VSC_A._GUEDES</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>A. Guedes</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>5</v>
+      </c>
+      <c r="E13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F13" t="n">
         <v>3</v>
       </c>
-      <c r="F4" t="n">
-        <v>6</v>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>50.0%</t>
-        </is>
-      </c>
-      <c r="H4" t="n">
-        <v>1</v>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>46.2%</t>
-        </is>
-      </c>
-      <c r="J4" t="n">
-        <v>1</v>
-      </c>
-      <c r="K4" t="n">
-        <v>1</v>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>20.0%</t>
+        </is>
+      </c>
+      <c r="H13" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="J13" t="n">
+        <v>1</v>
+      </c>
+      <c r="K13" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>VSC_M._DRUMWRIGHT</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>M. Drumwright</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>5</v>
+      </c>
+      <c r="E14" t="n">
+        <v>1</v>
+      </c>
+      <c r="F14" t="n">
+        <v>3</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>20.0%</t>
+        </is>
+      </c>
+      <c r="H14" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>21.7%</t>
+        </is>
+      </c>
+      <c r="J14" t="n">
+        <v>3</v>
+      </c>
+      <c r="K14" t="n">
+        <v>2</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K4"/>
+  <autoFilter ref="A1:K14"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/site/leagues/betclic/2026_2027/xlsx/shot_packs/shot_pack_VSC.xlsx
+++ b/site/leagues/betclic/2026_2027/xlsx/shot_packs/shot_pack_VSC.xlsx
@@ -21,14 +21,14 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'overview'!$A$1:$W$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'alerts'!$A$1:$B$6</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'players_volume'!$A$1:$S$10</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'players_eff'!$A$1:$S$7</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'players_3pt_volume'!$A$1:$N$10</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'players_3pt_pct'!$A$1:$N$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'players_volume'!$A$1:$S$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'players_eff'!$A$1:$S$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'players_3pt_volume'!$A$1:$N$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'players_3pt_pct'!$A$1:$N$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'team_zones'!$A$1:$I$7</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'preferred_areas'!$A$1:$P$10</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'player_zones_volume'!$A$1:$K$14</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'player_zones_pct'!$A$1:$K$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'preferred_areas'!$A$1:$P$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'player_zones_volume'!$A$1:$K$17</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'player_zones_pct'!$A$1:$K$10</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -590,42 +590,42 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>128</v>
+        <v>205</v>
       </c>
       <c r="D2" t="n">
-        <v>53</v>
+        <v>79</v>
       </c>
       <c r="E2" t="n">
-        <v>122</v>
+        <v>183</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>41.4%</t>
+          <t>38.5%</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>80</v>
+        <v>131</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>46.2%</t>
+          <t>41.2%</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>48</v>
+        <v>74</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>33.8%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>37.5%</t>
+          <t>36.1%</t>
         </is>
       </c>
       <c r="L2" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -633,11 +633,11 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>42</v>
+        <v>72</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>59.5%</t>
+          <t>52.8%</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -646,27 +646,27 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>36</v>
+        <v>56</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>30.6%</t>
+          <t>32.1%</t>
         </is>
       </c>
       <c r="S2" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="T2" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="U2" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="V2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -681,7 +681,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K6"/>
+  <dimension ref="A1:K10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -757,12 +757,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>VSC_M._HOUGE</t>
+          <t>VSC_M._DRUMWRIGHT</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>M. Houge</t>
+          <t>M. Drumwright</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -771,29 +771,29 @@
         </is>
       </c>
       <c r="D2" t="n">
+        <v>12</v>
+      </c>
+      <c r="E2" t="n">
         <v>8</v>
       </c>
-      <c r="E2" t="n">
-        <v>5</v>
-      </c>
       <c r="F2" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>62.5%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>88.9%</t>
+          <t>32.4%</t>
         </is>
       </c>
       <c r="J2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K2" t="n">
         <v>1</v>
@@ -802,31 +802,31 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>VSC_K._WARNER</t>
+          <t>VSC_R._STEIN</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>K. Warner</t>
+          <t>R. Stein</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="D3" t="n">
+        <v>14</v>
+      </c>
+      <c r="E3" t="n">
         <v>8</v>
       </c>
-      <c r="E3" t="n">
-        <v>3</v>
-      </c>
       <c r="F3" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>37.5%</t>
+          <t>57.1%</t>
         </is>
       </c>
       <c r="H3" t="n">
@@ -834,52 +834,52 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>47.1%</t>
+          <t>38.9%</t>
         </is>
       </c>
       <c r="J3" t="n">
         <v>1</v>
       </c>
       <c r="K3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>VSC_D._RUNGE</t>
+          <t>VSC_M._HOUGE</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>D. Runge</t>
+          <t>M. Houge</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E4" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="F4" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>46.7%</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>56.2%</t>
+          <t>68.2%</t>
         </is>
       </c>
       <c r="J4" t="n">
@@ -906,81 +906,261 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="E5" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="F5" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>27.3%</t>
+          <t>38.9%</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>54.5%</t>
         </is>
       </c>
       <c r="J5" t="n">
         <v>1</v>
       </c>
       <c r="K5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>VSC_D._RUNGE</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>D. Runge</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>9</v>
+      </c>
+      <c r="E6" t="n">
+        <v>3</v>
+      </c>
+      <c r="F6" t="n">
+        <v>9</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>52.9%</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
+        <v>1</v>
+      </c>
+      <c r="K6" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
           <t>VSC_M._DRUMWRIGHT</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>M. Drumwright</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>9</v>
+      </c>
+      <c r="E7" t="n">
+        <v>3</v>
+      </c>
+      <c r="F7" t="n">
+        <v>9</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="H7" t="n">
+        <v>1</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>24.3%</t>
+        </is>
+      </c>
+      <c r="J7" t="n">
+        <v>3</v>
+      </c>
+      <c r="K7" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>VSC_K._WARNER</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>K. Warner</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>19</v>
+      </c>
+      <c r="E8" t="n">
+        <v>5</v>
+      </c>
+      <c r="F8" t="n">
+        <v>15</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>26.3%</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>55.9%</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
+        <v>1</v>
+      </c>
+      <c r="K8" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>VSC_T._SIMAO</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>T. Simao</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
         <is>
           <t>Paint Non-RA</t>
         </is>
       </c>
-      <c r="D6" t="n">
-        <v>8</v>
-      </c>
-      <c r="E6" t="n">
-        <v>1</v>
-      </c>
-      <c r="F6" t="n">
+      <c r="D9" t="n">
+        <v>9</v>
+      </c>
+      <c r="E9" t="n">
         <v>2</v>
       </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>12.5%</t>
-        </is>
-      </c>
-      <c r="H6" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>34.8%</t>
-        </is>
-      </c>
-      <c r="J6" t="n">
-        <v>1</v>
-      </c>
-      <c r="K6" t="n">
+      <c r="F9" t="n">
+        <v>4</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>22.2%</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>27.3%</t>
+        </is>
+      </c>
+      <c r="J9" t="n">
+        <v>2</v>
+      </c>
+      <c r="K9" t="n">
         <v>3</v>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>VSC_M._DRUMWRIGHT</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>M. Drumwright</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>13</v>
+      </c>
+      <c r="E10" t="n">
+        <v>2</v>
+      </c>
+      <c r="F10" t="n">
+        <v>4</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>15.4%</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>35.1%</t>
+        </is>
+      </c>
+      <c r="J10" t="n">
+        <v>1</v>
+      </c>
+      <c r="K10" t="n">
+        <v>3</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:K6"/>
+  <autoFilter ref="A1:K10"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1018,7 +1198,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Maior volume: M. Drumwright (23 L)</t>
+          <t>Maior volume: M. Drumwright (37 L)</t>
         </is>
       </c>
     </row>
@@ -1030,7 +1210,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Maior volume 3pt: D. Runge (10 3PA)</t>
+          <t>Maior volume 3pt: K. Warner (23 3PA)</t>
         </is>
       </c>
     </row>
@@ -1054,7 +1234,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Zona mais usada: Restricted Area (42 L)</t>
+          <t>Zona mais usada: Restricted Area (72 L)</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1246,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Zona mais eficaz: Restricted Area (59.5%)</t>
+          <t>Zona mais eficaz: Restricted Area (52.8%)</t>
         </is>
       </c>
     </row>
@@ -1082,7 +1262,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S10"/>
+  <dimension ref="A1:S11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -1215,69 +1395,69 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="D2" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="E2" t="n">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>30.4%</t>
+          <t>37.8%</t>
         </is>
       </c>
       <c r="G2" t="n">
+        <v>9</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>24.3%</t>
+        </is>
+      </c>
+      <c r="J2" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="L2" t="n">
+        <v>13</v>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>15.4%</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="O2" t="n">
+        <v>12</v>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>66.7%</t>
+        </is>
+      </c>
+      <c r="Q2" t="n">
+        <v>1</v>
+      </c>
+      <c r="R2" t="n">
         <v>5</v>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>20.0%</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>21.7%</t>
-        </is>
-      </c>
-      <c r="J2" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>Paint Non-RA</t>
-        </is>
-      </c>
-      <c r="L2" t="n">
-        <v>8</v>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>12.5%</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>Restricted Area</t>
-        </is>
-      </c>
-      <c r="O2" t="n">
-        <v>7</v>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>57.1%</t>
-        </is>
-      </c>
-      <c r="Q2" t="n">
-        <v>1</v>
-      </c>
-      <c r="R2" t="n">
-        <v>6</v>
-      </c>
       <c r="S2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3">
@@ -1292,30 +1472,30 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="D3" t="n">
+        <v>16</v>
+      </c>
+      <c r="E3" t="n">
+        <v>35</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>44.4%</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
         <v>10</v>
       </c>
-      <c r="E3" t="n">
-        <v>22</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>45.5%</t>
-        </is>
-      </c>
-      <c r="G3" t="n">
-        <v>7</v>
-      </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>28.6%</t>
+          <t>30.0%</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>31.8%</t>
+          <t>27.8%</t>
         </is>
       </c>
       <c r="J3" t="n">
@@ -1327,16 +1507,16 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>83.3%</t>
+          <t>57.1%</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>Mid-Range</t>
+          <t>Paint Non-RA</t>
         </is>
       </c>
       <c r="O3" t="n">
@@ -1344,263 +1524,263 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="Q3" t="n">
         <v>2</v>
       </c>
       <c r="R3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>VSC_T._SIMAO</t>
+          <t>VSC_K._WARNER</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>T. Simao</t>
+          <t>K. Warner</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="D4" t="n">
+        <v>11</v>
+      </c>
+      <c r="E4" t="n">
+        <v>28</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>32.4%</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>23</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>26.1%</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>67.6%</t>
+        </is>
+      </c>
+      <c r="J4" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="L4" t="n">
+        <v>19</v>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>26.3%</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="O4" t="n">
         <v>7</v>
       </c>
-      <c r="E4" t="n">
-        <v>16</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>31.8%</t>
-        </is>
-      </c>
-      <c r="G4" t="n">
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>57.1%</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>3</v>
+      </c>
+      <c r="R4" t="n">
         <v>6</v>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>33.3%</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>27.3%</t>
-        </is>
-      </c>
-      <c r="J4" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>Restricted Area</t>
-        </is>
-      </c>
-      <c r="L4" t="n">
-        <v>11</v>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>27.3%</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
-        </is>
-      </c>
-      <c r="O4" t="n">
-        <v>5</v>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>40.0%</t>
-        </is>
-      </c>
-      <c r="Q4" t="n">
-        <v>2</v>
-      </c>
-      <c r="R4" t="n">
-        <v>5</v>
-      </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>VSC_K._WARNER</t>
+          <t>VSC_T._SIMAO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>K. Warner</t>
+          <t>T. Simao</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="D5" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E5" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>41.2%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="G5" t="n">
+        <v>6</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>18.2%</t>
+        </is>
+      </c>
+      <c r="J5" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="L5" t="n">
+        <v>18</v>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>38.9%</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="O5" t="n">
         <v>9</v>
       </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>33.3%</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>52.9%</t>
-        </is>
-      </c>
-      <c r="J5" t="n">
-        <v>1</v>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
-        </is>
-      </c>
-      <c r="L5" t="n">
-        <v>8</v>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>37.5%</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>Restricted Area</t>
-        </is>
-      </c>
-      <c r="O5" t="n">
-        <v>5</v>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="Q5" t="n">
         <v>4</v>
       </c>
       <c r="R5" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="S5" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>VSC_D._RUNGE</t>
+          <t>VSC_M._HOUGE</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>D. Runge</t>
+          <t>M. Houge</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="D6" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E6" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>45.5%</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>75.0%</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>62.5%</t>
+          <t>18.2%</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="L6" t="n">
+        <v>15</v>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>46.7%</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
           <t>Above the Break 3</t>
         </is>
       </c>
-      <c r="L6" t="n">
-        <v>9</v>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>33.3%</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>Restricted Area</t>
-        </is>
-      </c>
       <c r="O6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="Q6" t="n">
         <v>5</v>
       </c>
       <c r="R6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S6" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>VSC_A._GUEDES</t>
+          <t>VSC_D._RUNGE</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>A. Guedes</t>
+          <t>D. Runge</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D7" t="n">
         <v>8</v>
@@ -1610,24 +1790,24 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>53.3%</t>
+          <t>47.1%</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>53.3%</t>
+          <t>58.8%</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -1635,132 +1815,136 @@
         </is>
       </c>
       <c r="L7" t="n">
+        <v>9</v>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="O7" t="n">
         <v>5</v>
       </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>20.0%</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>Paint Non-RA</t>
-        </is>
-      </c>
-      <c r="O7" t="n">
-        <v>3</v>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>60.0%</t>
         </is>
       </c>
       <c r="Q7" t="n">
         <v>6</v>
       </c>
       <c r="R7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>VSC_M._HOUGE</t>
+          <t>VSC_A._GUEDES</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>M. Houge</t>
+          <t>A. Guedes</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D8" t="n">
+        <v>8</v>
+      </c>
+      <c r="E8" t="n">
+        <v>20</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>53.3%</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>8</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>53.3%</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="L8" t="n">
         <v>5</v>
       </c>
-      <c r="E8" t="n">
-        <v>10</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>55.6%</t>
-        </is>
-      </c>
-      <c r="G8" t="n">
-        <v>0</v>
-      </c>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="J8" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>Restricted Area</t>
-        </is>
-      </c>
-      <c r="L8" t="n">
-        <v>8</v>
-      </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>62.5%</t>
+          <t>20.0%</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>Mid-Range</t>
+          <t>Paint Non-RA</t>
         </is>
       </c>
       <c r="O8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="Q8" t="n">
         <v>7</v>
       </c>
       <c r="R8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="S8" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>VSC_R._COSTA</t>
+          <t>VSC_S._VERDE</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>R. Costa</t>
+          <t>S. Verde</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1773,11 +1957,11 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>28.6%</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -1785,20 +1969,20 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>Corner 3 Left</t>
+          <t>Mid-Range</t>
         </is>
       </c>
       <c r="O9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P9" t="inlineStr">
         <is>
@@ -1809,81 +1993,154 @@
         <v>8</v>
       </c>
       <c r="R9" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="S9" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>VSC_S._VERDE</t>
+          <t>VSC_R._COSTA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>S. Verde</t>
+          <t>R. Costa</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>2</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
           <t>0.0%</t>
         </is>
       </c>
-      <c r="G10" t="n">
-        <v>1</v>
-      </c>
-      <c r="H10" t="inlineStr">
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>66.7%</t>
+        </is>
+      </c>
+      <c r="J10" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="L10" t="n">
+        <v>1</v>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>Corner 3 Left</t>
+        </is>
+      </c>
+      <c r="O10" t="n">
+        <v>1</v>
+      </c>
+      <c r="P10" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="J10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>Corner 3 Right</t>
-        </is>
-      </c>
-      <c r="L10" t="n">
-        <v>1</v>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr"/>
-      <c r="O10" t="inlineStr"/>
-      <c r="P10" t="inlineStr"/>
       <c r="Q10" t="n">
         <v>9</v>
       </c>
       <c r="R10" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="S10" t="n">
         <v>8</v>
       </c>
     </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>VSC_D._ALEVOK</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>D. Alevok</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>1</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="G11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="L11" t="n">
+        <v>1</v>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr"/>
+      <c r="Q11" t="n">
+        <v>10</v>
+      </c>
+      <c r="R11" t="n">
+        <v>9</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:S10"/>
+  <autoFilter ref="A1:S11"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1894,7 +2151,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S7"/>
+  <dimension ref="A1:S8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -2086,10 +2343,10 @@
         <v>1</v>
       </c>
       <c r="R2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="S2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3">
@@ -2108,11 +2365,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>47.1%</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F3" t="n">
         <v>8</v>
@@ -2130,7 +2387,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>62.5%</t>
+          <t>58.8%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -2152,32 +2409,32 @@
         </is>
       </c>
       <c r="O3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>60.0%</t>
         </is>
       </c>
       <c r="Q3" t="n">
         <v>2</v>
       </c>
       <c r="R3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="S3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>VSC_R._STEIN</t>
+          <t>VSC_M._HOUGE</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>R. Stein</t>
+          <t>M. Houge</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -2195,19 +2452,19 @@
         <v>10</v>
       </c>
       <c r="G4" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H4" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>28.6%</t>
+          <t>75.0%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>31.8%</t>
+          <t>18.2%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -2216,45 +2473,45 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>83.3%</t>
+          <t>46.7%</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>Mid-Range</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="O4" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="Q4" t="n">
         <v>3</v>
       </c>
       <c r="R4" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>VSC_K._WARNER</t>
+          <t>VSC_R._STEIN</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>K. Warner</t>
+          <t>R. Stein</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -2262,97 +2519,97 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>41.2%</t>
+          <t>44.4%</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>17</v>
+        <v>36</v>
       </c>
       <c r="F5" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="G5" t="n">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="H5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>30.0%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>52.9%</t>
+          <t>27.8%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="L5" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>37.5%</t>
+          <t>57.1%</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>Paint Non-RA</t>
         </is>
       </c>
       <c r="O5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="S5" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>VSC_T._SIMAO</t>
+          <t>VSC_M._DRUMWRIGHT</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>T. Simao</t>
+          <t>M. Drumwright</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>31.8%</t>
+          <t>37.8%</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="F6" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="G6" t="n">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="H6" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -2361,97 +2618,97 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>27.3%</t>
+          <t>24.3%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="L6" t="n">
+        <v>13</v>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>15.4%</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
           <t>Restricted Area</t>
         </is>
       </c>
-      <c r="L6" t="n">
-        <v>11</v>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>27.3%</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
-        </is>
-      </c>
       <c r="O6" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="Q6" t="n">
         <v>5</v>
       </c>
       <c r="R6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>VSC_M._DRUMWRIGHT</t>
+          <t>VSC_K._WARNER</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>M. Drumwright</t>
+          <t>K. Warner</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>30.4%</t>
+          <t>32.4%</t>
         </is>
       </c>
       <c r="E7" t="n">
+        <v>34</v>
+      </c>
+      <c r="F7" t="n">
+        <v>11</v>
+      </c>
+      <c r="G7" t="n">
+        <v>28</v>
+      </c>
+      <c r="H7" t="n">
         <v>23</v>
       </c>
-      <c r="F7" t="n">
-        <v>7</v>
-      </c>
-      <c r="G7" t="n">
-        <v>15</v>
-      </c>
-      <c r="H7" t="n">
-        <v>5</v>
-      </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>26.1%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>21.7%</t>
+          <t>67.6%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="L7" t="n">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>26.3%</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -2471,14 +2728,91 @@
         <v>6</v>
       </c>
       <c r="R7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="S7" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>VSC_T._SIMAO</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>T. Simao</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>33</v>
+      </c>
+      <c r="F8" t="n">
+        <v>11</v>
+      </c>
+      <c r="G8" t="n">
+        <v>24</v>
+      </c>
+      <c r="H8" t="n">
         <v>6</v>
       </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>18.2%</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="L8" t="n">
+        <v>18</v>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>38.9%</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="O8" t="n">
+        <v>9</v>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>22.2%</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>7</v>
+      </c>
+      <c r="R8" t="n">
+        <v>4</v>
+      </c>
+      <c r="S8" t="n">
+        <v>4</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:S7"/>
+  <autoFilter ref="A1:S8"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2489,7 +2823,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N10"/>
+  <dimension ref="A1:N11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -2583,38 +2917,38 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>VSC_D._RUNGE</t>
+          <t>VSC_K._WARNER</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>D. Runge</t>
+          <t>K. Warner</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="D2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>26.1%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>62.5%</t>
+          <t>67.6%</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>16</v>
+        <v>34</v>
       </c>
       <c r="H2" t="n">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="I2" t="n">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -2622,55 +2956,55 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>26.3%</t>
         </is>
       </c>
       <c r="M2" t="n">
         <v>1</v>
       </c>
       <c r="N2" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>VSC_K._WARNER</t>
+          <t>VSC_D._RUNGE</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>K. Warner</t>
+          <t>D. Runge</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>52.9%</t>
+          <t>58.8%</t>
         </is>
       </c>
       <c r="G3" t="n">
         <v>17</v>
       </c>
       <c r="H3" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="I3" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -2678,11 +3012,11 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>37.5%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="M3" t="n">
@@ -2695,281 +3029,281 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>VSC_A._GUEDES</t>
+          <t>VSC_R._STEIN</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>A. Guedes</t>
+          <t>R. Stein</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>30.0%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>53.3%</t>
+          <t>27.8%</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="H4" t="n">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="I4" t="n">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="K4" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>57.1%</t>
         </is>
       </c>
       <c r="M4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N4" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>VSC_R._STEIN</t>
+          <t>VSC_M._DRUMWRIGHT</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>R. Stein</t>
+          <t>M. Drumwright</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>28.6%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>31.8%</t>
+          <t>24.3%</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="H5" t="n">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="I5" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>Paint Non-RA</t>
         </is>
       </c>
       <c r="K5" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>83.3%</t>
+          <t>15.4%</t>
         </is>
       </c>
       <c r="M5" t="n">
         <v>4</v>
       </c>
       <c r="N5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>VSC_T._SIMAO</t>
+          <t>VSC_A._GUEDES</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>T. Simao</t>
+          <t>A. Guedes</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>27.3%</t>
+          <t>53.3%</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="H6" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="I6" t="n">
-        <v>0.7</v>
+        <v>1.3</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="K6" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>27.3%</t>
+          <t>20.0%</t>
         </is>
       </c>
       <c r="M6" t="n">
         <v>5</v>
       </c>
       <c r="N6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>VSC_M._DRUMWRIGHT</t>
+          <t>VSC_T._SIMAO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>M. Drumwright</t>
+          <t>T. Simao</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>21.7%</t>
+          <t>18.2%</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="H7" t="n">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="I7" t="n">
         <v>0.7</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="K7" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>38.9%</t>
         </is>
       </c>
       <c r="M7" t="n">
         <v>6</v>
       </c>
       <c r="N7" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>VSC_R._COSTA</t>
+          <t>VSC_M._HOUGE</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>R. Costa</t>
+          <t>M. Houge</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>75.0%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>18.2%</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>3</v>
+        <v>22</v>
       </c>
       <c r="H8" t="n">
-        <v>2</v>
+        <v>23</v>
       </c>
       <c r="I8" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="K8" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>46.7%</t>
         </is>
       </c>
       <c r="M8" t="n">
         <v>7</v>
       </c>
       <c r="N8" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -2984,7 +3318,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
@@ -2996,11 +3330,11 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>28.6%</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -3010,11 +3344,11 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Corner 3 Right</t>
+          <t>Paint Non-RA</t>
         </is>
       </c>
       <c r="K9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
@@ -3025,61 +3359,117 @@
         <v>8</v>
       </c>
       <c r="N9" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>VSC_M._HOUGE</t>
+          <t>VSC_R._COSTA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>M. Houge</t>
+          <t>R. Costa</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D10" t="n">
         <v>0</v>
       </c>
-      <c r="E10" t="inlineStr"/>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
       <c r="F10" t="inlineStr">
         <is>
+          <t>66.7%</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>3</v>
+      </c>
+      <c r="H10" t="n">
+        <v>2</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="K10" t="n">
+        <v>1</v>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="M10" t="n">
+        <v>8</v>
+      </c>
+      <c r="N10" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>VSC_D._ALEVOK</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>D. Alevok</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr">
+        <is>
           <t>0.0%</t>
         </is>
       </c>
-      <c r="G10" t="n">
-        <v>9</v>
-      </c>
-      <c r="H10" t="n">
+      <c r="G11" t="n">
+        <v>1</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="K11" t="n">
+        <v>1</v>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="M11" t="n">
         <v>10</v>
       </c>
-      <c r="I10" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>Restricted Area</t>
-        </is>
-      </c>
-      <c r="K10" t="n">
-        <v>8</v>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>62.5%</t>
-        </is>
-      </c>
-      <c r="M10" t="n">
-        <v>9</v>
-      </c>
-      <c r="N10" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N10"/>
+  <autoFilter ref="A1:N11"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3090,10 +3480,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N2"/>
+  <dimension ref="A1:N4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="1" max="1"/>
     <col width="13" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
@@ -3205,11 +3595,11 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>62.5%</t>
+          <t>58.8%</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H2" t="n">
         <v>20</v>
@@ -3231,14 +3621,126 @@
         </is>
       </c>
       <c r="M2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N2" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>VSC_R._STEIN</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>R. Stein</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>10</v>
+      </c>
+      <c r="D3" t="n">
+        <v>3</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>30.0%</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>27.8%</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>36</v>
+      </c>
+      <c r="H3" t="n">
+        <v>35</v>
+      </c>
+      <c r="I3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="K3" t="n">
+        <v>14</v>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>57.1%</t>
+        </is>
+      </c>
+      <c r="M3" t="n">
         <v>2</v>
       </c>
+      <c r="N3" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>VSC_K._WARNER</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>K. Warner</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>23</v>
+      </c>
+      <c r="D4" t="n">
+        <v>6</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>26.1%</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>67.6%</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>34</v>
+      </c>
+      <c r="H4" t="n">
+        <v>28</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="K4" t="n">
+        <v>19</v>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>26.3%</t>
+        </is>
+      </c>
+      <c r="M4" t="n">
+        <v>1</v>
+      </c>
+      <c r="N4" t="n">
+        <v>7</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N2"/>
+  <autoFilter ref="A1:N4"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3317,25 +3819,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>42</v>
+        <v>72</v>
       </c>
       <c r="C2" t="n">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="D2" t="n">
-        <v>50</v>
+        <v>76</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>59.5%</t>
+          <t>52.8%</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>32.8%</t>
+          <t>35.1%</t>
         </is>
       </c>
       <c r="H2" t="n">
@@ -3352,25 +3854,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>36</v>
+        <v>56</v>
       </c>
       <c r="C3" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="D3" t="n">
-        <v>33</v>
+        <v>54</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>30.6%</t>
+          <t>32.1%</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>28.1%</t>
+          <t>27.3%</t>
         </is>
       </c>
       <c r="H3" t="n">
@@ -3387,32 +3889,32 @@
         </is>
       </c>
       <c r="B4" t="n">
+        <v>42</v>
+      </c>
+      <c r="C4" t="n">
+        <v>12</v>
+      </c>
+      <c r="D4" t="n">
         <v>24</v>
       </c>
-      <c r="C4" t="n">
-        <v>9</v>
-      </c>
-      <c r="D4" t="n">
-        <v>18</v>
-      </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>37.5%</t>
+          <t>28.6%</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>18.8%</t>
+          <t>20.5%</t>
         </is>
       </c>
       <c r="H4" t="n">
         <v>3</v>
       </c>
       <c r="I4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5">
@@ -3422,32 +3924,32 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="C5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D5" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>21.4%</t>
+          <t>23.5%</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>10.9%</t>
+          <t>8.3%</t>
         </is>
       </c>
       <c r="H5" t="n">
         <v>4</v>
       </c>
       <c r="I5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6">
@@ -3457,7 +3959,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C6" t="n">
         <v>4</v>
@@ -3467,15 +3969,15 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>6.2%</t>
+          <t>4.9%</t>
         </is>
       </c>
       <c r="H6" t="n">
@@ -3492,32 +3994,32 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D7" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>37.5%</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>0.8</v>
+        <v>1.1</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>3.1%</t>
+          <t>3.9%</t>
         </is>
       </c>
       <c r="H7" t="n">
         <v>6</v>
       </c>
       <c r="I7" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -3532,7 +4034,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P10"/>
+  <dimension ref="A1:P11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -3652,11 +4154,11 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>15.4%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -3665,11 +4167,11 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>57.1%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -3678,31 +4180,31 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="L2" t="n">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>30.4%</t>
+          <t>37.8%</t>
         </is>
       </c>
       <c r="N2" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="P2" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="3">
@@ -3722,16 +4224,16 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>83.3%</t>
+          <t>57.1%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mid-Range</t>
+          <t>Paint Non-RA</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -3739,36 +4241,36 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Mid-Range</t>
+        </is>
+      </c>
+      <c r="J3" t="n">
+        <v>6</v>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
           <t>33.3%</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
-        </is>
-      </c>
-      <c r="J3" t="n">
-        <v>4</v>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>25.0%</t>
-        </is>
-      </c>
       <c r="L3" t="n">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>45.5%</t>
+          <t>44.4%</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>28.6%</t>
+          <t>30.0%</t>
         </is>
       </c>
       <c r="P3" t="n">
@@ -3778,38 +4280,38 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>VSC_T._SIMAO</t>
+          <t>VSC_K._WARNER</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>T. Simao</t>
+          <t>K. Warner</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>19</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>26.3%</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
           <t>Restricted Area</t>
         </is>
       </c>
-      <c r="D4" t="n">
-        <v>11</v>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>27.3%</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
-        </is>
-      </c>
       <c r="G4" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>57.1%</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -3818,93 +4320,93 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="L4" t="n">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>31.8%</t>
+          <t>32.4%</t>
         </is>
       </c>
       <c r="N4" t="n">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>26.1%</t>
         </is>
       </c>
       <c r="P4" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>VSC_K._WARNER</t>
+          <t>VSC_T._SIMAO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>K. Warner</t>
+          <t>T. Simao</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>18</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>38.9%</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>9</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>22.2%</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
           <t>Above the Break 3</t>
         </is>
       </c>
-      <c r="D5" t="n">
-        <v>8</v>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>37.5%</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Restricted Area</t>
-        </is>
-      </c>
-      <c r="G5" t="n">
+      <c r="J5" t="n">
         <v>5</v>
       </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>80.0%</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>Paint Non-RA</t>
-        </is>
-      </c>
-      <c r="J5" t="n">
-        <v>3</v>
-      </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="L5" t="n">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>41.2%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="N5" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -3912,88 +4414,88 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>VSC_D._RUNGE</t>
+          <t>VSC_M._HOUGE</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>D. Runge</t>
+          <t>M. Houge</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>15</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>46.7%</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
           <t>Above the Break 3</t>
         </is>
       </c>
-      <c r="D6" t="n">
-        <v>9</v>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>33.3%</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Restricted Area</t>
-        </is>
-      </c>
       <c r="G6" t="n">
+        <v>3</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>66.7%</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
+        <v>2</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="L6" t="n">
+        <v>22</v>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>45.5%</t>
+        </is>
+      </c>
+      <c r="N6" t="n">
         <v>4</v>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="O6" t="inlineStr">
         <is>
           <t>75.0%</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>Corner 3 Left</t>
-        </is>
-      </c>
-      <c r="J6" t="n">
-        <v>1</v>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="L6" t="n">
-        <v>16</v>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>50.0%</t>
-        </is>
-      </c>
-      <c r="N6" t="n">
-        <v>10</v>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>40.0%</t>
-        </is>
-      </c>
       <c r="P6" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>VSC_A._GUEDES</t>
+          <t>VSC_D._RUNGE</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>A. Guedes</t>
+          <t>D. Runge</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -4002,124 +4504,138 @@
         </is>
       </c>
       <c r="D7" t="n">
+        <v>9</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
         <v>5</v>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>20.0%</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Paint Non-RA</t>
-        </is>
-      </c>
-      <c r="G7" t="n">
-        <v>3</v>
-      </c>
       <c r="H7" t="inlineStr">
         <is>
+          <t>60.0%</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Corner 3 Left</t>
+        </is>
+      </c>
+      <c r="J7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
           <t>100.0%</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>Mid-Range</t>
-        </is>
-      </c>
-      <c r="J7" t="n">
-        <v>3</v>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
       <c r="L7" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>53.3%</t>
+          <t>47.1%</t>
         </is>
       </c>
       <c r="N7" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="P7" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>VSC_M._HOUGE</t>
+          <t>VSC_A._GUEDES</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>M. Houge</t>
+          <t>A. Guedes</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="D8" t="n">
+        <v>5</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>20.0%</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>3</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Mid-Range</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
+        <v>3</v>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="L8" t="n">
+        <v>15</v>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>53.3%</t>
+        </is>
+      </c>
+      <c r="N8" t="n">
         <v>8</v>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>62.5%</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Mid-Range</t>
-        </is>
-      </c>
-      <c r="G8" t="n">
-        <v>1</v>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="n">
-        <v>9</v>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>55.6%</t>
-        </is>
-      </c>
-      <c r="N8" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" t="inlineStr"/>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
       <c r="P8" t="n">
-        <v>1.1</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>VSC_R._COSTA</t>
+          <t>VSC_S._VERDE</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>R. Costa</t>
+          <t>S. Verde</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -4128,20 +4644,20 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Corner 3 Left</t>
+          <t>Mid-Range</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -4150,7 +4666,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Corner 3 Right</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="J9" t="n">
@@ -4162,11 +4678,11 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="N9" t="n">
@@ -4178,61 +4694,127 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>0.7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>VSC_S._VERDE</t>
+          <t>VSC_R._COSTA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>S. Verde</t>
+          <t>R. Costa</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>1</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Corner 3 Left</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>1</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
           <t>Corner 3 Right</t>
         </is>
       </c>
-      <c r="D10" t="n">
-        <v>1</v>
-      </c>
-      <c r="E10" t="inlineStr">
+      <c r="J10" t="n">
+        <v>1</v>
+      </c>
+      <c r="K10" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
       <c r="L10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="N10" t="n">
+        <v>2</v>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
           <t>0.0%</t>
         </is>
       </c>
-      <c r="N10" t="n">
-        <v>1</v>
-      </c>
-      <c r="O10" t="inlineStr">
+      <c r="P10" t="n">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>VSC_D._ALEVOK</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>D. Alevok</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>1</v>
+      </c>
+      <c r="E11" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
-      <c r="P10" t="n">
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="n">
+        <v>1</v>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="N11" t="n">
         <v>0</v>
       </c>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:P10"/>
+  <autoFilter ref="A1:P11"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4243,7 +4825,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K14"/>
+  <dimension ref="A1:K17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -4319,91 +4901,91 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>VSC_T._SIMAO</t>
+          <t>VSC_K._WARNER</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>T. Simao</t>
+          <t>K. Warner</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="E2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F2" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>27.3%</t>
+          <t>26.3%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>55.9%</t>
         </is>
       </c>
       <c r="J2" t="n">
         <v>1</v>
       </c>
       <c r="K2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>VSC_D._RUNGE</t>
+          <t>VSC_T._SIMAO</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>D. Runge</t>
+          <t>T. Simao</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="E3" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="F3" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>38.9%</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>56.2%</t>
+          <t>54.5%</t>
         </is>
       </c>
       <c r="J3" t="n">
         <v>1</v>
       </c>
       <c r="K3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4">
@@ -4423,25 +5005,25 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="E4" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F4" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>62.5%</t>
+          <t>46.7%</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>1.2</v>
+        <v>0.9</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>88.9%</t>
+          <t>68.2%</t>
         </is>
       </c>
       <c r="J4" t="n">
@@ -4454,31 +5036,31 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>VSC_K._WARNER</t>
+          <t>VSC_R._STEIN</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>K. Warner</t>
+          <t>R. Stein</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="D5" t="n">
+        <v>14</v>
+      </c>
+      <c r="E5" t="n">
         <v>8</v>
       </c>
-      <c r="E5" t="n">
-        <v>3</v>
-      </c>
       <c r="F5" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>37.5%</t>
+          <t>57.1%</t>
         </is>
       </c>
       <c r="H5" t="n">
@@ -4486,14 +5068,14 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>47.1%</t>
+          <t>38.9%</t>
         </is>
       </c>
       <c r="J5" t="n">
         <v>1</v>
       </c>
       <c r="K5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -4513,25 +5095,25 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>15.4%</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>34.8%</t>
+          <t>35.1%</t>
         </is>
       </c>
       <c r="J6" t="n">
@@ -4558,25 +5140,25 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="E7" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F7" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>57.1%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>1.1</v>
+        <v>1.3</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>30.4%</t>
+          <t>32.4%</t>
         </is>
       </c>
       <c r="J7" t="n">
@@ -4589,72 +5171,72 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>VSC_R._STEIN</t>
+          <t>VSC_D._RUNGE</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>R. Stein</t>
+          <t>D. Runge</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E8" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F8" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>83.3%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>1.7</v>
+        <v>1</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>27.3%</t>
+          <t>52.9%</t>
         </is>
       </c>
       <c r="J8" t="n">
         <v>1</v>
       </c>
       <c r="K8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>VSC_R._STEIN</t>
+          <t>VSC_M._DRUMWRIGHT</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>R. Stein</t>
+          <t>M. Drumwright</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Mid-Range</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F9" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -4662,15 +5244,15 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>27.3%</t>
+          <t>24.3%</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K9" t="n">
         <v>2</v>
@@ -4679,84 +5261,84 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>VSC_K._WARNER</t>
+          <t>VSC_T._SIMAO</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>K. Warner</t>
+          <t>T. Simao</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>Paint Non-RA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E10" t="n">
+        <v>2</v>
+      </c>
+      <c r="F10" t="n">
         <v>4</v>
       </c>
-      <c r="F10" t="n">
-        <v>8</v>
-      </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>1.6</v>
+        <v>0.4</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>29.4%</t>
+          <t>27.3%</t>
         </is>
       </c>
       <c r="J10" t="n">
         <v>2</v>
       </c>
       <c r="K10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>VSC_T._SIMAO</t>
+          <t>VSC_K._WARNER</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>T. Simao</t>
+          <t>K. Warner</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E11" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F11" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>57.1%</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>22.7%</t>
+          <t>20.6%</t>
         </is>
       </c>
       <c r="J11" t="n">
@@ -4769,12 +5351,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>VSC_T._SIMAO</t>
+          <t>VSC_R._STEIN</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>T. Simao</t>
+          <t>R. Stein</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -4783,126 +5365,261 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F12" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>22.7%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="J12" t="n">
         <v>2</v>
       </c>
       <c r="K12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>VSC_A._GUEDES</t>
+          <t>VSC_R._STEIN</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>A. Guedes</t>
+          <t>R. Stein</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Mid-Range</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F13" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K13" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>VSC_M._DRUMWRIGHT</t>
+          <t>VSC_D._RUNGE</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>M. Drumwright</t>
+          <t>D. Runge</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="D14" t="n">
         <v>5</v>
       </c>
       <c r="E14" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F14" t="n">
+        <v>6</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>60.0%</t>
+        </is>
+      </c>
+      <c r="H14" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>29.4%</t>
+        </is>
+      </c>
+      <c r="J14" t="n">
+        <v>2</v>
+      </c>
+      <c r="K14" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>VSC_R._STEIN</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>R. Stein</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>5</v>
+      </c>
+      <c r="E15" t="n">
+        <v>2</v>
+      </c>
+      <c r="F15" t="n">
+        <v>6</v>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>40.0%</t>
+        </is>
+      </c>
+      <c r="H15" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>13.9%</t>
+        </is>
+      </c>
+      <c r="J15" t="n">
+        <v>4</v>
+      </c>
+      <c r="K15" t="n">
         <v>3</v>
       </c>
-      <c r="G14" t="inlineStr">
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>VSC_T._SIMAO</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>T. Simao</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>5</v>
+      </c>
+      <c r="E16" t="n">
+        <v>2</v>
+      </c>
+      <c r="F16" t="n">
+        <v>6</v>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>40.0%</t>
+        </is>
+      </c>
+      <c r="H16" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>15.2%</t>
+        </is>
+      </c>
+      <c r="J16" t="n">
+        <v>3</v>
+      </c>
+      <c r="K16" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>VSC_A._GUEDES</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>A. Guedes</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>5</v>
+      </c>
+      <c r="E17" t="n">
+        <v>1</v>
+      </c>
+      <c r="F17" t="n">
+        <v>3</v>
+      </c>
+      <c r="G17" t="inlineStr">
         <is>
           <t>20.0%</t>
         </is>
       </c>
-      <c r="H14" t="n">
+      <c r="H17" t="n">
         <v>0.6</v>
       </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>21.7%</t>
-        </is>
-      </c>
-      <c r="J14" t="n">
-        <v>3</v>
-      </c>
-      <c r="K14" t="n">
-        <v>2</v>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="J17" t="n">
+        <v>1</v>
+      </c>
+      <c r="K17" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K14"/>
+  <autoFilter ref="A1:K17"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/site/leagues/betclic/2026_2027/xlsx/shot_packs/shot_pack_VSC.xlsx
+++ b/site/leagues/betclic/2026_2027/xlsx/shot_packs/shot_pack_VSC.xlsx
@@ -22,13 +22,13 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'overview'!$A$1:$W$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'alerts'!$A$1:$B$6</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'players_volume'!$A$1:$S$11</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'players_eff'!$A$1:$S$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'players_eff'!$A$1:$S$9</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'players_3pt_volume'!$A$1:$N$11</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'players_3pt_pct'!$A$1:$N$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'players_3pt_pct'!$A$1:$N$7</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'team_zones'!$A$1:$I$7</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'preferred_areas'!$A$1:$P$11</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'player_zones_volume'!$A$1:$K$17</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'player_zones_pct'!$A$1:$K$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'player_zones_volume'!$A$1:$K$19</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'player_zones_pct'!$A$1:$K$13</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -590,13 +590,13 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>205</v>
+        <v>270</v>
       </c>
       <c r="D2" t="n">
-        <v>79</v>
+        <v>104</v>
       </c>
       <c r="E2" t="n">
-        <v>183</v>
+        <v>241</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -604,24 +604,24 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>131</v>
+        <v>166</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>41.2%</t>
+          <t>42.8%</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>74</v>
+        <v>104</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>33.8%</t>
+          <t>31.7%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>36.1%</t>
+          <t>38.5%</t>
         </is>
       </c>
       <c r="L2" t="n">
@@ -633,11 +633,11 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>72</v>
+        <v>95</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>52.8%</t>
+          <t>53.7%</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -646,7 +646,7 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>56</v>
+        <v>78</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
@@ -654,7 +654,7 @@
         </is>
       </c>
       <c r="S2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T2" t="n">
         <v>11</v>
@@ -666,7 +666,7 @@
         <v>7</v>
       </c>
       <c r="W2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -681,7 +681,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K10"/>
+  <dimension ref="A1:K13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -757,12 +757,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>VSC_M._DRUMWRIGHT</t>
+          <t>VSC_D._RUNGE</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>M. Drumwright</t>
+          <t>D. Runge</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -771,25 +771,25 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E2" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F2" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>62.5%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>32.4%</t>
+          <t>36.4%</t>
         </is>
       </c>
       <c r="J2" t="n">
@@ -802,12 +802,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>VSC_R._STEIN</t>
+          <t>VSC_K._WARNER</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>R. Stein</t>
+          <t>K. Warner</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -816,29 +816,29 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="E3" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F3" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>57.1%</t>
+          <t>62.5%</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>38.9%</t>
+          <t>19.0%</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K3" t="n">
         <v>1</v>
@@ -847,12 +847,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>VSC_M._HOUGE</t>
+          <t>VSC_R._STEIN</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>M. Houge</t>
+          <t>R. Stein</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -861,25 +861,25 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E4" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="F4" t="n">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>46.7%</t>
+          <t>61.1%</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>0.9</v>
+        <v>1.2</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>68.2%</t>
+          <t>41.9%</t>
         </is>
       </c>
       <c r="J4" t="n">
@@ -906,62 +906,62 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="E5" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="F5" t="n">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>38.9%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>54.5%</t>
+          <t>55.0%</t>
         </is>
       </c>
       <c r="J5" t="n">
         <v>1</v>
       </c>
       <c r="K5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>VSC_D._RUNGE</t>
+          <t>VSC_M._DRUMWRIGHT</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>D. Runge</t>
+          <t>M. Drumwright</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="D6" t="n">
+        <v>18</v>
+      </c>
+      <c r="E6" t="n">
         <v>9</v>
       </c>
-      <c r="E6" t="n">
-        <v>3</v>
-      </c>
       <c r="F6" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="H6" t="n">
@@ -969,70 +969,70 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>52.9%</t>
+          <t>36.0%</t>
         </is>
       </c>
       <c r="J6" t="n">
         <v>1</v>
       </c>
       <c r="K6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>VSC_M._DRUMWRIGHT</t>
+          <t>VSC_M._HOUGE</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>M. Drumwright</t>
+          <t>M. Houge</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="E7" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="F7" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>38.9%</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>24.3%</t>
+          <t>69.2%</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>VSC_K._WARNER</t>
+          <t>VSC_M._DRUMWRIGHT</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>K. Warner</t>
+          <t>M. Drumwright</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1041,29 +1041,29 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="E8" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F8" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>26.3%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>55.9%</t>
+          <t>24.0%</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K8" t="n">
         <v>2</v>
@@ -1072,57 +1072,57 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>VSC_T._SIMAO</t>
+          <t>VSC_K._WARNER</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>T. Simao</t>
+          <t>K. Warner</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="E9" t="n">
+        <v>8</v>
+      </c>
+      <c r="F9" t="n">
+        <v>24</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>32.0%</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
+        <v>1</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>59.5%</t>
+        </is>
+      </c>
+      <c r="J9" t="n">
+        <v>1</v>
+      </c>
+      <c r="K9" t="n">
         <v>2</v>
-      </c>
-      <c r="F9" t="n">
-        <v>4</v>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>22.2%</t>
-        </is>
-      </c>
-      <c r="H9" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>27.3%</t>
-        </is>
-      </c>
-      <c r="J9" t="n">
-        <v>2</v>
-      </c>
-      <c r="K9" t="n">
-        <v>3</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>VSC_M._DRUMWRIGHT</t>
+          <t>VSC_T._SIMAO</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>M. Drumwright</t>
+          <t>T. Simao</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1131,36 +1131,171 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E10" t="n">
+        <v>3</v>
+      </c>
+      <c r="F10" t="n">
+        <v>6</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>30.0%</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>25.0%</t>
+        </is>
+      </c>
+      <c r="J10" t="n">
         <v>2</v>
-      </c>
-      <c r="F10" t="n">
-        <v>4</v>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>15.4%</t>
-        </is>
-      </c>
-      <c r="H10" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>35.1%</t>
-        </is>
-      </c>
-      <c r="J10" t="n">
-        <v>1</v>
       </c>
       <c r="K10" t="n">
         <v>3</v>
       </c>
     </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>VSC_D._RUNGE</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>D. Runge</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>11</v>
+      </c>
+      <c r="E11" t="n">
+        <v>3</v>
+      </c>
+      <c r="F11" t="n">
+        <v>9</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>27.3%</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="J11" t="n">
+        <v>1</v>
+      </c>
+      <c r="K11" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>VSC_M._DRUMWRIGHT</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>M. Drumwright</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>16</v>
+      </c>
+      <c r="E12" t="n">
+        <v>2</v>
+      </c>
+      <c r="F12" t="n">
+        <v>4</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>12.5%</t>
+        </is>
+      </c>
+      <c r="H12" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>32.0%</t>
+        </is>
+      </c>
+      <c r="J12" t="n">
+        <v>2</v>
+      </c>
+      <c r="K12" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>VSC_S._VERDE</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>S. Verde</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>8</v>
+      </c>
+      <c r="E13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F13" t="n">
+        <v>3</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>12.5%</t>
+        </is>
+      </c>
+      <c r="H13" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>38.1%</t>
+        </is>
+      </c>
+      <c r="J13" t="n">
+        <v>1</v>
+      </c>
+      <c r="K13" t="n">
+        <v>2</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:K10"/>
+  <autoFilter ref="A1:K13"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1198,7 +1333,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Maior volume: M. Drumwright (37 L)</t>
+          <t>Maior volume: M. Drumwright (50 L)</t>
         </is>
       </c>
     </row>
@@ -1210,7 +1345,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Maior volume 3pt: K. Warner (23 3PA)</t>
+          <t>Maior volume 3pt: K. Warner (30 3PA)</t>
         </is>
       </c>
     </row>
@@ -1222,7 +1357,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Mais eficaz: A. Guedes (1.3 pts/shot)</t>
+          <t>Mais eficaz: D. Runge (1.1 pts/shot)</t>
         </is>
       </c>
     </row>
@@ -1234,7 +1369,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Zona mais usada: Restricted Area (72 L)</t>
+          <t>Zona mais usada: Restricted Area (95 L)</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1381,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Zona mais eficaz: Restricted Area (52.8%)</t>
+          <t>Zona mais eficaz: Restricted Area (53.7%)</t>
         </is>
       </c>
     </row>
@@ -1395,21 +1530,21 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="D2" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E2" t="n">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>37.8%</t>
+          <t>32.0%</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -1418,46 +1553,46 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>24.3%</t>
+          <t>24.0%</t>
         </is>
       </c>
       <c r="J2" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="L2" t="n">
+        <v>18</v>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
           <t>Paint Non-RA</t>
         </is>
       </c>
-      <c r="L2" t="n">
-        <v>13</v>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>15.4%</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>Restricted Area</t>
-        </is>
-      </c>
       <c r="O2" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>12.5%</t>
         </is>
       </c>
       <c r="Q2" t="n">
         <v>1</v>
       </c>
       <c r="R2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="S2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3">
@@ -1472,34 +1607,34 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="D3" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="E3" t="n">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>44.4%</t>
+          <t>48.8%</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>30.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>27.8%</t>
+          <t>27.9%</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -1507,34 +1642,34 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>57.1%</t>
+          <t>61.1%</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="O3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>42.9%</t>
         </is>
       </c>
       <c r="Q3" t="n">
         <v>2</v>
       </c>
       <c r="R3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="S3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4">
@@ -1549,34 +1684,34 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="D4" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="E4" t="n">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>32.4%</t>
+          <t>35.7%</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>26.1%</t>
+          <t>30.0%</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>67.6%</t>
+          <t>71.4%</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -1584,11 +1719,11 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>26.3%</t>
+          <t>32.0%</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -1597,18 +1732,18 @@
         </is>
       </c>
       <c r="O4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>57.1%</t>
+          <t>62.5%</t>
         </is>
       </c>
       <c r="Q4" t="n">
         <v>3</v>
       </c>
       <c r="R4" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -1626,34 +1761,34 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="D5" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="E5" t="n">
-        <v>24</v>
+        <v>37</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>42.5%</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>37.5%</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>18.2%</t>
+          <t>20.0%</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -1661,11 +1796,11 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>38.9%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -1674,21 +1809,21 @@
         </is>
       </c>
       <c r="O5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>30.0%</t>
         </is>
       </c>
       <c r="Q5" t="n">
         <v>4</v>
       </c>
       <c r="R5" t="n">
+        <v>5</v>
+      </c>
+      <c r="S5" t="n">
         <v>7</v>
-      </c>
-      <c r="S5" t="n">
-        <v>6</v>
       </c>
     </row>
     <row r="6">
@@ -1703,7 +1838,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="D6" t="n">
         <v>10</v>
@@ -1713,7 +1848,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>45.5%</t>
+          <t>38.5%</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1726,11 +1861,11 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>18.2%</t>
+          <t>15.4%</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -1738,11 +1873,11 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>46.7%</t>
+          <t>38.9%</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1762,10 +1897,10 @@
         <v>5</v>
       </c>
       <c r="R6" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="S6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="7">
@@ -1780,69 +1915,69 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="D7" t="n">
+        <v>10</v>
+      </c>
+      <c r="E7" t="n">
+        <v>24</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>45.5%</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>12</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>54.5%</t>
+        </is>
+      </c>
+      <c r="J7" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="L7" t="n">
+        <v>11</v>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>27.3%</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="O7" t="n">
         <v>8</v>
       </c>
-      <c r="E7" t="n">
-        <v>20</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>47.1%</t>
-        </is>
-      </c>
-      <c r="G7" t="n">
-        <v>10</v>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>40.0%</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>58.8%</t>
-        </is>
-      </c>
-      <c r="J7" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
-        </is>
-      </c>
-      <c r="L7" t="n">
-        <v>9</v>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>33.3%</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>Restricted Area</t>
-        </is>
-      </c>
-      <c r="O7" t="n">
-        <v>5</v>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>62.5%</t>
         </is>
       </c>
       <c r="Q7" t="n">
         <v>6</v>
       </c>
       <c r="R7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8">
@@ -1857,34 +1992,34 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="D8" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E8" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>53.3%</t>
+          <t>42.9%</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>30.8%</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>53.3%</t>
+          <t>61.9%</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -1892,34 +2027,34 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Corner 3 Right</t>
         </is>
       </c>
       <c r="O8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="Q8" t="n">
         <v>7</v>
       </c>
       <c r="R8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -1934,69 +2069,69 @@
         </is>
       </c>
       <c r="C9" t="n">
+        <v>21</v>
+      </c>
+      <c r="D9" t="n">
+        <v>5</v>
+      </c>
+      <c r="E9" t="n">
+        <v>12</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>23.8%</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>11</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>18.2%</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>52.4%</t>
+        </is>
+      </c>
+      <c r="J9" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="L9" t="n">
+        <v>8</v>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>12.5%</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>Mid-Range</t>
+        </is>
+      </c>
+      <c r="O9" t="n">
+        <v>5</v>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>40.0%</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
         <v>7</v>
       </c>
-      <c r="D9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="G9" t="n">
-        <v>2</v>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>28.6%</t>
-        </is>
-      </c>
-      <c r="J9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>Paint Non-RA</t>
-        </is>
-      </c>
-      <c r="L9" t="n">
-        <v>3</v>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>Mid-Range</t>
-        </is>
-      </c>
-      <c r="O9" t="n">
-        <v>2</v>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="Q9" t="n">
+      <c r="R9" t="n">
         <v>8</v>
       </c>
-      <c r="R9" t="n">
-        <v>9</v>
-      </c>
       <c r="S9" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10">
@@ -2073,7 +2208,7 @@
         <v>8</v>
       </c>
       <c r="S10" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="11">
@@ -2088,7 +2223,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
@@ -2119,7 +2254,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -2133,7 +2268,7 @@
         <v>10</v>
       </c>
       <c r="R11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -2151,7 +2286,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S8"/>
+  <dimension ref="A1:S9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -2275,152 +2410,152 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>VSC_A._GUEDES</t>
+          <t>VSC_D._RUNGE</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>A. Guedes</t>
+          <t>D. Runge</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>53.3%</t>
+          <t>45.5%</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="F2" t="n">
+        <v>10</v>
+      </c>
+      <c r="G2" t="n">
+        <v>24</v>
+      </c>
+      <c r="H2" t="n">
+        <v>12</v>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>54.5%</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="L2" t="n">
+        <v>11</v>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>27.3%</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="O2" t="n">
         <v>8</v>
       </c>
-      <c r="G2" t="n">
-        <v>20</v>
-      </c>
-      <c r="H2" t="n">
-        <v>8</v>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>50.0%</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>53.3%</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
-        </is>
-      </c>
-      <c r="L2" t="n">
-        <v>5</v>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>20.0%</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>Paint Non-RA</t>
-        </is>
-      </c>
-      <c r="O2" t="n">
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>62.5%</t>
+        </is>
+      </c>
+      <c r="Q2" t="n">
+        <v>1</v>
+      </c>
+      <c r="R2" t="n">
+        <v>6</v>
+      </c>
+      <c r="S2" t="n">
         <v>3</v>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="Q2" t="n">
-        <v>1</v>
-      </c>
-      <c r="R2" t="n">
-        <v>7</v>
-      </c>
-      <c r="S2" t="n">
-        <v>2</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>VSC_D._RUNGE</t>
+          <t>VSC_R._STEIN</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>D. Runge</t>
+          <t>R. Stein</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>47.1%</t>
+          <t>48.8%</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>17</v>
+        <v>43</v>
       </c>
       <c r="F3" t="n">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="G3" t="n">
-        <v>20</v>
+        <v>46</v>
       </c>
       <c r="H3" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>58.8%</t>
+          <t>27.9%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="L3" t="n">
+        <v>18</v>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>61.1%</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
           <t>Above the Break 3</t>
         </is>
       </c>
-      <c r="L3" t="n">
-        <v>9</v>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>33.3%</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>Restricted Area</t>
-        </is>
-      </c>
       <c r="O3" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>42.9%</t>
         </is>
       </c>
       <c r="Q3" t="n">
         <v>2</v>
       </c>
       <c r="R3" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="S3" t="n">
         <v>3</v>
@@ -2429,12 +2564,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>VSC_M._HOUGE</t>
+          <t>VSC_A._GUEDES</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>M. Houge</t>
+          <t>A. Guedes</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -2442,97 +2577,97 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>45.5%</t>
+          <t>42.9%</t>
         </is>
       </c>
       <c r="E4" t="n">
+        <v>21</v>
+      </c>
+      <c r="F4" t="n">
+        <v>9</v>
+      </c>
+      <c r="G4" t="n">
         <v>22</v>
       </c>
-      <c r="F4" t="n">
-        <v>10</v>
-      </c>
-      <c r="G4" t="n">
-        <v>23</v>
-      </c>
       <c r="H4" t="n">
+        <v>13</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>30.8%</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>61.9%</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="L4" t="n">
+        <v>6</v>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>16.7%</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>Corner 3 Right</t>
+        </is>
+      </c>
+      <c r="O4" t="n">
         <v>4</v>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>75.0%</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>18.2%</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>Restricted Area</t>
-        </is>
-      </c>
-      <c r="L4" t="n">
-        <v>15</v>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>46.7%</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
-        </is>
-      </c>
-      <c r="O4" t="n">
-        <v>3</v>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="Q4" t="n">
         <v>3</v>
       </c>
       <c r="R4" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="S4" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>VSC_R._STEIN</t>
+          <t>VSC_K._WARNER</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>R. Stein</t>
+          <t>K. Warner</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>44.4%</t>
+          <t>35.7%</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="F5" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G5" t="n">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="H5" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -2541,208 +2676,208 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>27.8%</t>
+          <t>71.4%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="L5" t="n">
+        <v>25</v>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>32.0%</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
           <t>Restricted Area</t>
         </is>
       </c>
-      <c r="L5" t="n">
-        <v>14</v>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>57.1%</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>Paint Non-RA</t>
-        </is>
-      </c>
       <c r="O5" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>62.5%</t>
         </is>
       </c>
       <c r="Q5" t="n">
         <v>4</v>
       </c>
       <c r="R5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>VSC_M._DRUMWRIGHT</t>
+          <t>VSC_T._SIMAO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>M. Drumwright</t>
+          <t>T. Simao</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>37.8%</t>
+          <t>42.5%</t>
         </is>
       </c>
       <c r="E6" t="n">
+        <v>40</v>
+      </c>
+      <c r="F6" t="n">
+        <v>17</v>
+      </c>
+      <c r="G6" t="n">
         <v>37</v>
       </c>
-      <c r="F6" t="n">
-        <v>14</v>
-      </c>
-      <c r="G6" t="n">
-        <v>31</v>
-      </c>
       <c r="H6" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>37.5%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>24.3%</t>
+          <t>20.0%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="L6" t="n">
+        <v>22</v>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
           <t>Paint Non-RA</t>
         </is>
       </c>
-      <c r="L6" t="n">
-        <v>13</v>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>15.4%</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>Restricted Area</t>
-        </is>
-      </c>
       <c r="O6" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>30.0%</t>
         </is>
       </c>
       <c r="Q6" t="n">
         <v>5</v>
       </c>
       <c r="R6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="S6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>VSC_K._WARNER</t>
+          <t>VSC_M._HOUGE</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>K. Warner</t>
+          <t>M. Houge</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>32.4%</t>
+          <t>38.5%</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="F7" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G7" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="H7" t="n">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>26.1%</t>
+          <t>75.0%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>67.6%</t>
+          <t>15.4%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="L7" t="n">
+        <v>18</v>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>38.9%</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
           <t>Above the Break 3</t>
         </is>
       </c>
-      <c r="L7" t="n">
-        <v>19</v>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>26.3%</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>Restricted Area</t>
-        </is>
-      </c>
       <c r="O7" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>57.1%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="Q7" t="n">
         <v>6</v>
       </c>
       <c r="R7" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="S7" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>VSC_T._SIMAO</t>
+          <t>VSC_M._DRUMWRIGHT</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>T. Simao</t>
+          <t>M. Drumwright</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -2750,29 +2885,29 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
+          <t>32.0%</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>50</v>
+      </c>
+      <c r="F8" t="n">
+        <v>16</v>
+      </c>
+      <c r="G8" t="n">
+        <v>36</v>
+      </c>
+      <c r="H8" t="n">
+        <v>12</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
           <t>33.3%</t>
         </is>
       </c>
-      <c r="E8" t="n">
-        <v>33</v>
-      </c>
-      <c r="F8" t="n">
-        <v>11</v>
-      </c>
-      <c r="G8" t="n">
-        <v>24</v>
-      </c>
-      <c r="H8" t="n">
-        <v>6</v>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>33.3%</t>
-        </is>
-      </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>18.2%</t>
+          <t>24.0%</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -2785,7 +2920,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>38.9%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -2794,25 +2929,102 @@
         </is>
       </c>
       <c r="O8" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>12.5%</t>
         </is>
       </c>
       <c r="Q8" t="n">
         <v>7</v>
       </c>
       <c r="R8" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="S8" t="n">
-        <v>4</v>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>VSC_S._VERDE</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>S. Verde</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>23.8%</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>21</v>
+      </c>
+      <c r="F9" t="n">
+        <v>5</v>
+      </c>
+      <c r="G9" t="n">
+        <v>12</v>
+      </c>
+      <c r="H9" t="n">
+        <v>11</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>18.2%</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>52.4%</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="L9" t="n">
+        <v>8</v>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>12.5%</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>Mid-Range</t>
+        </is>
+      </c>
+      <c r="O9" t="n">
+        <v>5</v>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>40.0%</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>8</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7</v>
+      </c>
+      <c r="S9" t="n">
+        <v>8</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:S8"/>
+  <autoFilter ref="A1:S9"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2926,29 +3138,29 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="D2" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>26.1%</t>
+          <t>30.0%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>67.6%</t>
+          <t>71.4%</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="H2" t="n">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="I2" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -2956,11 +3168,11 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>26.3%</t>
+          <t>32.0%</t>
         </is>
       </c>
       <c r="M2" t="n">
@@ -2973,38 +3185,38 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>VSC_D._RUNGE</t>
+          <t>VSC_A._GUEDES</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>D. Runge</t>
+          <t>A. Guedes</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="D3" t="n">
         <v>4</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>30.8%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>58.8%</t>
+          <t>61.9%</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="H3" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="I3" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -3012,167 +3224,167 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="M3" t="n">
         <v>2</v>
       </c>
       <c r="N3" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>VSC_R._STEIN</t>
+          <t>VSC_M._DRUMWRIGHT</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>R. Stein</t>
+          <t>M. Drumwright</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D4" t="n">
+        <v>4</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>24.0%</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>50</v>
+      </c>
+      <c r="H4" t="n">
+        <v>36</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="K4" t="n">
+        <v>18</v>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="M4" t="n">
         <v>3</v>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>30.0%</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>27.8%</t>
-        </is>
-      </c>
-      <c r="G4" t="n">
-        <v>36</v>
-      </c>
-      <c r="H4" t="n">
-        <v>35</v>
-      </c>
-      <c r="I4" t="n">
-        <v>1</v>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>Restricted Area</t>
-        </is>
-      </c>
-      <c r="K4" t="n">
-        <v>14</v>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>57.1%</t>
-        </is>
-      </c>
-      <c r="M4" t="n">
-        <v>2</v>
-      </c>
       <c r="N4" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>VSC_M._DRUMWRIGHT</t>
+          <t>VSC_R._STEIN</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>M. Drumwright</t>
+          <t>R. Stein</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D5" t="n">
+        <v>4</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>27.9%</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>43</v>
+      </c>
+      <c r="H5" t="n">
+        <v>46</v>
+      </c>
+      <c r="I5" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="K5" t="n">
+        <v>18</v>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>61.1%</t>
+        </is>
+      </c>
+      <c r="M5" t="n">
         <v>3</v>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>33.3%</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>24.3%</t>
-        </is>
-      </c>
-      <c r="G5" t="n">
-        <v>37</v>
-      </c>
-      <c r="H5" t="n">
-        <v>31</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>Paint Non-RA</t>
-        </is>
-      </c>
-      <c r="K5" t="n">
-        <v>13</v>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>15.4%</t>
-        </is>
-      </c>
-      <c r="M5" t="n">
-        <v>4</v>
-      </c>
       <c r="N5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>VSC_A._GUEDES</t>
+          <t>VSC_D._RUNGE</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>A. Guedes</t>
+          <t>D. Runge</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D6" t="n">
         <v>4</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>53.3%</t>
+          <t>54.5%</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H6" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="I6" t="n">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -3180,186 +3392,186 @@
         </is>
       </c>
       <c r="K6" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>27.3%</t>
         </is>
       </c>
       <c r="M6" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>VSC_T._SIMAO</t>
+          <t>VSC_S._VERDE</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>T. Simao</t>
+          <t>S. Verde</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="D7" t="n">
         <v>2</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>18.2%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>18.2%</t>
+          <t>52.4%</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="H7" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="I7" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="K7" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>38.9%</t>
+          <t>12.5%</t>
         </is>
       </c>
       <c r="M7" t="n">
         <v>6</v>
       </c>
       <c r="N7" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>VSC_M._HOUGE</t>
+          <t>VSC_T._SIMAO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>M. Houge</t>
+          <t>T. Simao</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D8" t="n">
         <v>3</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>37.5%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>18.2%</t>
+          <t>20.0%</t>
         </is>
       </c>
       <c r="G8" t="n">
+        <v>40</v>
+      </c>
+      <c r="H8" t="n">
+        <v>37</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="K8" t="n">
         <v>22</v>
       </c>
-      <c r="H8" t="n">
-        <v>23</v>
-      </c>
-      <c r="I8" t="n">
-        <v>1</v>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>Restricted Area</t>
-        </is>
-      </c>
-      <c r="K8" t="n">
-        <v>15</v>
-      </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>46.7%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="M8" t="n">
         <v>7</v>
       </c>
       <c r="N8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>VSC_S._VERDE</t>
+          <t>VSC_M._HOUGE</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>S. Verde</t>
+          <t>M. Houge</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>75.0%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>28.6%</t>
+          <t>15.4%</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>7</v>
+        <v>26</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="K9" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>38.9%</t>
         </is>
       </c>
       <c r="M9" t="n">
         <v>8</v>
       </c>
       <c r="N9" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -3412,10 +3624,10 @@
         </is>
       </c>
       <c r="M10" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="N10" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="11">
@@ -3442,7 +3654,7 @@
         </is>
       </c>
       <c r="G11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
@@ -3456,7 +3668,7 @@
         </is>
       </c>
       <c r="K11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
@@ -3480,11 +3692,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N4"/>
+  <dimension ref="A1:N7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="15" customWidth="1" min="1" max="1"/>
-    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
@@ -3574,54 +3786,54 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>VSC_D._RUNGE</t>
+          <t>VSC_M._DRUMWRIGHT</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>D. Runge</t>
+          <t>M. Drumwright</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D2" t="n">
         <v>4</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>58.8%</t>
+          <t>24.0%</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>17</v>
+        <v>50</v>
       </c>
       <c r="H2" t="n">
-        <v>20</v>
+        <v>36</v>
       </c>
       <c r="I2" t="n">
-        <v>1.2</v>
+        <v>0.7</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="K2" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="M2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N2" t="n">
         <v>3</v>
@@ -3639,108 +3851,276 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D3" t="n">
+        <v>4</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>27.9%</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>43</v>
+      </c>
+      <c r="H3" t="n">
+        <v>46</v>
+      </c>
+      <c r="I3" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="K3" t="n">
+        <v>18</v>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>61.1%</t>
+        </is>
+      </c>
+      <c r="M3" t="n">
         <v>3</v>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>30.0%</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>27.8%</t>
-        </is>
-      </c>
-      <c r="G3" t="n">
-        <v>36</v>
-      </c>
-      <c r="H3" t="n">
-        <v>35</v>
-      </c>
-      <c r="I3" t="n">
-        <v>1</v>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>Restricted Area</t>
-        </is>
-      </c>
-      <c r="K3" t="n">
-        <v>14</v>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>57.1%</t>
-        </is>
-      </c>
-      <c r="M3" t="n">
-        <v>2</v>
-      </c>
       <c r="N3" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>VSC_D._RUNGE</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>D. Runge</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>12</v>
+      </c>
+      <c r="D4" t="n">
+        <v>4</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>54.5%</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>22</v>
+      </c>
+      <c r="H4" t="n">
+        <v>24</v>
+      </c>
+      <c r="I4" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="K4" t="n">
+        <v>11</v>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>27.3%</t>
+        </is>
+      </c>
+      <c r="M4" t="n">
+        <v>3</v>
+      </c>
+      <c r="N4" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>VSC_A._GUEDES</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>A. Guedes</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>13</v>
+      </c>
+      <c r="D5" t="n">
+        <v>4</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>30.8%</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>61.9%</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>21</v>
+      </c>
+      <c r="H5" t="n">
+        <v>22</v>
+      </c>
+      <c r="I5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="K5" t="n">
+        <v>6</v>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>16.7%</t>
+        </is>
+      </c>
+      <c r="M5" t="n">
+        <v>2</v>
+      </c>
+      <c r="N5" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
           <t>VSC_K._WARNER</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>K. Warner</t>
         </is>
       </c>
-      <c r="C4" t="n">
-        <v>23</v>
-      </c>
-      <c r="D4" t="n">
+      <c r="C6" t="n">
+        <v>30</v>
+      </c>
+      <c r="D6" t="n">
+        <v>9</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>30.0%</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>71.4%</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>42</v>
+      </c>
+      <c r="H6" t="n">
+        <v>39</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="K6" t="n">
+        <v>25</v>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>32.0%</t>
+        </is>
+      </c>
+      <c r="M6" t="n">
+        <v>1</v>
+      </c>
+      <c r="N6" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>VSC_S._VERDE</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>S. Verde</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>11</v>
+      </c>
+      <c r="D7" t="n">
+        <v>2</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>18.2%</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>52.4%</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>21</v>
+      </c>
+      <c r="H7" t="n">
+        <v>12</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="K7" t="n">
+        <v>8</v>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>12.5%</t>
+        </is>
+      </c>
+      <c r="M7" t="n">
         <v>6</v>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>26.1%</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>67.6%</t>
-        </is>
-      </c>
-      <c r="G4" t="n">
-        <v>34</v>
-      </c>
-      <c r="H4" t="n">
-        <v>28</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
-        </is>
-      </c>
-      <c r="K4" t="n">
-        <v>19</v>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>26.3%</t>
-        </is>
-      </c>
-      <c r="M4" t="n">
-        <v>1</v>
-      </c>
-      <c r="N4" t="n">
-        <v>7</v>
+      <c r="N7" t="n">
+        <v>8</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N4"/>
+  <autoFilter ref="A1:N7"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3819,17 +4199,17 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>72</v>
+        <v>95</v>
       </c>
       <c r="C2" t="n">
-        <v>38</v>
+        <v>51</v>
       </c>
       <c r="D2" t="n">
-        <v>76</v>
+        <v>102</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>52.8%</t>
+          <t>53.7%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -3837,7 +4217,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>35.1%</t>
+          <t>35.2%</t>
         </is>
       </c>
       <c r="H2" t="n">
@@ -3854,13 +4234,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>56</v>
+        <v>78</v>
       </c>
       <c r="C3" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="D3" t="n">
-        <v>54</v>
+        <v>75</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -3872,7 +4252,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>27.3%</t>
+          <t>28.9%</t>
         </is>
       </c>
       <c r="H3" t="n">
@@ -3889,32 +4269,32 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="C4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D4" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>28.6%</t>
+          <t>26.5%</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>20.5%</t>
+          <t>18.1%</t>
         </is>
       </c>
       <c r="H4" t="n">
         <v>3</v>
       </c>
       <c r="I4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5">
@@ -3924,32 +4304,32 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="C5" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D5" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>23.5%</t>
+          <t>31.8%</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>8.3%</t>
+          <t>8.1%</t>
         </is>
       </c>
       <c r="H5" t="n">
         <v>4</v>
       </c>
       <c r="I5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6">
@@ -3959,25 +4339,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="C6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D6" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>35.7%</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>4.9%</t>
+          <t>5.2%</t>
         </is>
       </c>
       <c r="H6" t="n">
@@ -3994,7 +4374,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="C7" t="n">
         <v>3</v>
@@ -4004,22 +4384,22 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>37.5%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.1</v>
+        <v>0.8</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>3.9%</t>
+          <t>4.4%</t>
         </is>
       </c>
       <c r="H7" t="n">
         <v>6</v>
       </c>
       <c r="I7" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -4150,53 +4530,53 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>18</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
           <t>Paint Non-RA</t>
         </is>
       </c>
-      <c r="D2" t="n">
-        <v>13</v>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>15.4%</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Restricted Area</t>
-        </is>
-      </c>
       <c r="G2" t="n">
+        <v>16</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>12.5%</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="J2" t="n">
         <v>12</v>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>66.7%</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
-        </is>
-      </c>
-      <c r="J2" t="n">
-        <v>9</v>
-      </c>
       <c r="K2" t="inlineStr">
         <is>
           <t>33.3%</t>
         </is>
       </c>
       <c r="L2" t="n">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>37.8%</t>
+          <t>32.0%</t>
         </is>
       </c>
       <c r="N2" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
@@ -4204,7 +4584,7 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="3">
@@ -4224,24 +4604,24 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>57.1%</t>
+          <t>61.1%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>42.9%</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -4250,31 +4630,31 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
+          <t>42.9%</t>
+        </is>
+      </c>
+      <c r="L3" t="n">
+        <v>43</v>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>48.8%</t>
+        </is>
+      </c>
+      <c r="N3" t="n">
+        <v>12</v>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
           <t>33.3%</t>
         </is>
       </c>
-      <c r="L3" t="n">
-        <v>36</v>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>44.4%</t>
-        </is>
-      </c>
-      <c r="N3" t="n">
-        <v>10</v>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>30.0%</t>
-        </is>
-      </c>
       <c r="P3" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="4">
@@ -4294,11 +4674,11 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>26.3%</t>
+          <t>32.0%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -4307,16 +4687,16 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>57.1%</t>
+          <t>62.5%</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Corner 3 Right</t>
         </is>
       </c>
       <c r="J4" t="n">
@@ -4324,27 +4704,27 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="L4" t="n">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>32.4%</t>
+          <t>35.7%</t>
         </is>
       </c>
       <c r="N4" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>26.1%</t>
+          <t>30.0%</t>
         </is>
       </c>
       <c r="P4" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="5">
@@ -4364,11 +4744,11 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>38.9%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -4377,11 +4757,11 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>30.0%</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -4390,31 +4770,31 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="L5" t="n">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>42.5%</t>
         </is>
       </c>
       <c r="N5" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>37.5%</t>
         </is>
       </c>
       <c r="P5" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="6">
@@ -4434,11 +4814,11 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>46.7%</t>
+          <t>38.9%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -4460,7 +4840,7 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -4468,11 +4848,11 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>45.5%</t>
+          <t>38.5%</t>
         </is>
       </c>
       <c r="N6" t="n">
@@ -4484,7 +4864,7 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="7">
@@ -4504,57 +4884,57 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
+          <t>27.3%</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>8</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>62.5%</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Corner 3 Left</t>
+        </is>
+      </c>
+      <c r="J7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="L7" t="n">
+        <v>22</v>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>45.5%</t>
+        </is>
+      </c>
+      <c r="N7" t="n">
+        <v>12</v>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
           <t>33.3%</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Restricted Area</t>
-        </is>
-      </c>
-      <c r="G7" t="n">
-        <v>5</v>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>60.0%</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>Corner 3 Left</t>
-        </is>
-      </c>
-      <c r="J7" t="n">
-        <v>1</v>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="L7" t="n">
-        <v>17</v>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>47.1%</t>
-        </is>
-      </c>
-      <c r="N7" t="n">
-        <v>10</v>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>40.0%</t>
-        </is>
-      </c>
       <c r="P7" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="8">
@@ -4574,29 +4954,29 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
+          <t>Corner 3 Right</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>4</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>25.0%</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
           <t>Paint Non-RA</t>
-        </is>
-      </c>
-      <c r="G8" t="n">
-        <v>3</v>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>Mid-Range</t>
         </is>
       </c>
       <c r="J8" t="n">
@@ -4604,27 +4984,27 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="L8" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>53.3%</t>
+          <t>42.9%</t>
         </is>
       </c>
       <c r="N8" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>30.8%</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>1.3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -4640,61 +5020,61 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>8</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>12.5%</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Mid-Range</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>5</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>40.0%</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
           <t>Paint Non-RA</t>
         </is>
       </c>
-      <c r="D9" t="n">
-        <v>3</v>
-      </c>
-      <c r="E9" t="inlineStr">
+      <c r="J9" t="n">
+        <v>4</v>
+      </c>
+      <c r="K9" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Mid-Range</t>
-        </is>
-      </c>
-      <c r="G9" t="n">
-        <v>2</v>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
-        </is>
-      </c>
-      <c r="J9" t="n">
-        <v>1</v>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
       <c r="L9" t="n">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>23.8%</t>
         </is>
       </c>
       <c r="N9" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>18.2%</t>
         </is>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="10">
@@ -4784,7 +5164,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -4798,7 +5178,7 @@
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -4825,7 +5205,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K17"/>
+  <dimension ref="A1:K19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -4915,25 +5295,25 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="E2" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F2" t="n">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>26.3%</t>
+          <t>32.0%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>55.9%</t>
+          <t>59.5%</t>
         </is>
       </c>
       <c r="J2" t="n">
@@ -4960,43 +5340,43 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="E3" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="F3" t="n">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>38.9%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>54.5%</t>
+          <t>55.0%</t>
         </is>
       </c>
       <c r="J3" t="n">
         <v>1</v>
       </c>
       <c r="K3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>VSC_M._HOUGE</t>
+          <t>VSC_R._STEIN</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>M. Houge</t>
+          <t>R. Stein</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -5005,25 +5385,25 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E4" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="F4" t="n">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>46.7%</t>
+          <t>61.1%</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>0.9</v>
+        <v>1.2</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>68.2%</t>
+          <t>41.9%</t>
         </is>
       </c>
       <c r="J4" t="n">
@@ -5036,12 +5416,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>VSC_R._STEIN</t>
+          <t>VSC_M._DRUMWRIGHT</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>R. Stein</t>
+          <t>M. Drumwright</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -5050,25 +5430,25 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="E5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F5" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>57.1%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>38.9%</t>
+          <t>36.0%</t>
         </is>
       </c>
       <c r="J5" t="n">
@@ -5081,46 +5461,46 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>VSC_M._DRUMWRIGHT</t>
+          <t>VSC_M._HOUGE</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>M. Drumwright</t>
+          <t>M. Houge</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="E6" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="F6" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>15.4%</t>
+          <t>38.9%</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>0.3</v>
+        <v>0.8</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>35.1%</t>
+          <t>69.2%</t>
         </is>
       </c>
       <c r="J6" t="n">
         <v>1</v>
       </c>
       <c r="K6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -5136,47 +5516,47 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>Paint Non-RA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E7" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="F7" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>12.5%</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>1.3</v>
+        <v>0.2</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>32.4%</t>
+          <t>32.0%</t>
         </is>
       </c>
       <c r="J7" t="n">
         <v>2</v>
       </c>
       <c r="K7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>VSC_D._RUNGE</t>
+          <t>VSC_M._DRUMWRIGHT</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>D. Runge</t>
+          <t>M. Drumwright</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -5185,29 +5565,29 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E8" t="n">
+        <v>4</v>
+      </c>
+      <c r="F8" t="n">
+        <v>12</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
+        <v>1</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>24.0%</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
         <v>3</v>
-      </c>
-      <c r="F8" t="n">
-        <v>9</v>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>33.3%</t>
-        </is>
-      </c>
-      <c r="H8" t="n">
-        <v>1</v>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>52.9%</t>
-        </is>
-      </c>
-      <c r="J8" t="n">
-        <v>1</v>
       </c>
       <c r="K8" t="n">
         <v>2</v>
@@ -5216,12 +5596,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>VSC_M._DRUMWRIGHT</t>
+          <t>VSC_D._RUNGE</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>M. Drumwright</t>
+          <t>D. Runge</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -5230,7 +5610,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E9" t="n">
         <v>3</v>
@@ -5240,19 +5620,19 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>27.3%</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>24.3%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K9" t="n">
         <v>2</v>
@@ -5275,25 +5655,25 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F10" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>30.0%</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>27.3%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="J10" t="n">
@@ -5306,12 +5686,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>VSC_K._WARNER</t>
+          <t>VSC_D._RUNGE</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>K. Warner</t>
+          <t>D. Runge</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -5320,25 +5700,25 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E11" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F11" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>57.1%</t>
+          <t>62.5%</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>20.6%</t>
+          <t>36.4%</t>
         </is>
       </c>
       <c r="J11" t="n">
@@ -5351,136 +5731,136 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>VSC_R._STEIN</t>
+          <t>VSC_K._WARNER</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>R. Stein</t>
+          <t>K. Warner</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E12" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F12" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>62.5%</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>19.0%</t>
         </is>
       </c>
       <c r="J12" t="n">
         <v>2</v>
       </c>
       <c r="K12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>VSC_R._STEIN</t>
+          <t>VSC_S._VERDE</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>R. Stein</t>
+          <t>S. Verde</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Mid-Range</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F13" t="n">
+        <v>3</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>12.5%</t>
+        </is>
+      </c>
+      <c r="H13" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>38.1%</t>
+        </is>
+      </c>
+      <c r="J13" t="n">
+        <v>1</v>
+      </c>
+      <c r="K13" t="n">
         <v>2</v>
-      </c>
-      <c r="F13" t="n">
-        <v>4</v>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>33.3%</t>
-        </is>
-      </c>
-      <c r="H13" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>16.7%</t>
-        </is>
-      </c>
-      <c r="J13" t="n">
-        <v>2</v>
-      </c>
-      <c r="K13" t="n">
-        <v>4</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>VSC_D._RUNGE</t>
+          <t>VSC_R._STEIN</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>D. Runge</t>
+          <t>R. Stein</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E14" t="n">
         <v>3</v>
       </c>
       <c r="F14" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>42.9%</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>29.4%</t>
+          <t>16.3%</t>
         </is>
       </c>
       <c r="J14" t="n">
         <v>2</v>
       </c>
       <c r="K14" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="15">
@@ -5496,33 +5876,33 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Mid-Range</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E15" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F15" t="n">
         <v>6</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>42.9%</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>1.2</v>
+        <v>0.9</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>13.9%</t>
+          <t>16.3%</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K15" t="n">
         <v>3</v>
@@ -5531,95 +5911,185 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>VSC_T._SIMAO</t>
+          <t>VSC_R._STEIN</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>T. Simao</t>
+          <t>R. Stein</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Paint Non-RA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F16" t="n">
         <v>6</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>15.2%</t>
+          <t>14.0%</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>VSC_T._SIMAO</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>T. Simao</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>6</v>
+      </c>
+      <c r="E17" t="n">
+        <v>3</v>
+      </c>
+      <c r="F17" t="n">
+        <v>9</v>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="H17" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>15.0%</t>
+        </is>
+      </c>
+      <c r="J17" t="n">
+        <v>3</v>
+      </c>
+      <c r="K17" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>VSC_A._GUEDES</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>A. Guedes</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="C18" t="inlineStr">
         <is>
           <t>Above the Break 3</t>
         </is>
       </c>
-      <c r="D17" t="n">
+      <c r="D18" t="n">
+        <v>6</v>
+      </c>
+      <c r="E18" t="n">
+        <v>1</v>
+      </c>
+      <c r="F18" t="n">
+        <v>3</v>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>16.7%</t>
+        </is>
+      </c>
+      <c r="H18" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>28.6%</t>
+        </is>
+      </c>
+      <c r="J18" t="n">
+        <v>1</v>
+      </c>
+      <c r="K18" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>VSC_S._VERDE</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>S. Verde</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Mid-Range</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
         <v>5</v>
       </c>
-      <c r="E17" t="n">
-        <v>1</v>
-      </c>
-      <c r="F17" t="n">
-        <v>3</v>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>20.0%</t>
-        </is>
-      </c>
-      <c r="H17" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>33.3%</t>
-        </is>
-      </c>
-      <c r="J17" t="n">
-        <v>1</v>
-      </c>
-      <c r="K17" t="n">
+      <c r="E19" t="n">
+        <v>2</v>
+      </c>
+      <c r="F19" t="n">
+        <v>4</v>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>40.0%</t>
+        </is>
+      </c>
+      <c r="H19" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>23.8%</t>
+        </is>
+      </c>
+      <c r="J19" t="n">
+        <v>2</v>
+      </c>
+      <c r="K19" t="n">
         <v>1</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K17"/>
+  <autoFilter ref="A1:K19"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>